--- a/data/DatosGrafica_AdquirirQ1_20260525_113127.xlsx
+++ b/data/DatosGrafica_AdquirirQ1_20260525_113127.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RepositorioGit\proyectosPropios\learningTesting\testeos\ModeloTermicoBjt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RepositorioGit\proyectoTesis\ModelosBJT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE62627-44C5-4A71-8A96-973591D6E62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A92D0133-5CAA-4149-9766-5565986E5B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4635" yWindow="1875" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -9521,6 +9521,10 @@
         <f>(MAX(B:B)-MIN(B:B))/(_xlfn.MODE.SNGL(D:D)-MIN(D:D))</f>
         <v>0.76049999999999995</v>
       </c>
+      <c r="R19">
+        <f>MAX(B:B)</f>
+        <v>106</v>
+      </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20">

--- a/data/DatosGrafica_AdquirirQ1_20260525_113127.xlsx
+++ b/data/DatosGrafica_AdquirirQ1_20260525_113127.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RepositorioGit\proyectoTesis\ModelosBJT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A92D0133-5CAA-4149-9766-5565986E5B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643B6A79-7A03-4F7D-8499-93C498CC9ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -117,8771 +117,14 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Temperatura1</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$B$2:$B$1312</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1311"/>
-                <c:pt idx="0">
-                  <c:v>29.99</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>29.95</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>29.95</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>29.99</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>30.05</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>30.05</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>30.21</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>30.39</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>30.68</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>30.68</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>30.99</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>31.4</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>31.4</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>31.83</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>32.32</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>32.86</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>33.42</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>33.42</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>33.979999999999997</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>34.6</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>35.22</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>35.22</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>35.840000000000003</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>36.520000000000003</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>37.15</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>37.15</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>37.880000000000003</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>38.53</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>39.159999999999997</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>39.83</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>39.83</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>40.520000000000003</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>41.2</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>41.89</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>41.89</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>42.53</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>43.21</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>43.84</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>43.84</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>44.52</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>45.15</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>45.78</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>45.78</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>46.46</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>47.09</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>47.72</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>47.72</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>48.34</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>48.97</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>49.54</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>49.54</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>50.16</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>50.73</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>50.73</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>51.35</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>51.92</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>52.48</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>53.1</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>53.67</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>53.67</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>54.23</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>54.75</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>55.3</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>55.3</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>55.81</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>56.36</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>56.87</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>56.87</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>57.42</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>57.93</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>58.44</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>58.44</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>58.94</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>59.44</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>59.89</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>59.89</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>60.38</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>60.88</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>61.33</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>61.33</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>61.77</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>62.2</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>62.69</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>62.69</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>63.14</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>63.58</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>63.58</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>63.97</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>63.97</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>64.83</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>65.22</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>65.64</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>65.64</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>66.03</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>66.459999999999994</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>66.84</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>66.84</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>67.22</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>67.59</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>67.97</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>67.97</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>68.34</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>68.72</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>69.040000000000006</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>69.040000000000006</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>69.41</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>69.73</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>70.099999999999994</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>70.099999999999994</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>70.42</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>70.73</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>71.099999999999994</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>71.42</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>71.42</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>71.73</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>72.05</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>72.36</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>72.36</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>72.67</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>72.98</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>73.25</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>73.25</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>73.55</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>73.86</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>74.17</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>74.17</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>74.430000000000007</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>74.69</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>74.94</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>74.94</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>75.239999999999995</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>75.5</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>75.75</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>75.75</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>76</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>76.3</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>76.56</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>76.81</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>76.81</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>77.06</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>77.31</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>77.510000000000005</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>77.510000000000005</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>77.75</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>78.25</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>78.25</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>78.45</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>78.69</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>78.89</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>78.89</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>79.13</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>79.33</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>79.569999999999993</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>79.569999999999993</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>79.760000000000005</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>79.95</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>80.19</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>80.39</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>80.39</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>80.58</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>80.77</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>80.95</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>80.95</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>81.14</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>81.38</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>81.58</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>81.58</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>81.77</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>81.900000000000006</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>82.08</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>82.08</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>82.32</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>82.46</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>82.64</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>82.64</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>82.83</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>83.02</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>83.15</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>83.15</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>83.33</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>83.52</c:v>
-                </c:pt>
-                <c:pt idx="188">
-                  <c:v>83.65</c:v>
-                </c:pt>
-                <c:pt idx="189">
-                  <c:v>83.65</c:v>
-                </c:pt>
-                <c:pt idx="190">
-                  <c:v>83.83</c:v>
-                </c:pt>
-                <c:pt idx="191">
-                  <c:v>84.02</c:v>
-                </c:pt>
-                <c:pt idx="192">
-                  <c:v>84.15</c:v>
-                </c:pt>
-                <c:pt idx="193">
-                  <c:v>84.33</c:v>
-                </c:pt>
-                <c:pt idx="194">
-                  <c:v>84.33</c:v>
-                </c:pt>
-                <c:pt idx="195">
-                  <c:v>84.47</c:v>
-                </c:pt>
-                <c:pt idx="196">
-                  <c:v>84.59</c:v>
-                </c:pt>
-                <c:pt idx="197">
-                  <c:v>84.77</c:v>
-                </c:pt>
-                <c:pt idx="198">
-                  <c:v>84.77</c:v>
-                </c:pt>
-                <c:pt idx="199">
-                  <c:v>84.9</c:v>
-                </c:pt>
-                <c:pt idx="200">
-                  <c:v>85.08</c:v>
-                </c:pt>
-                <c:pt idx="201">
-                  <c:v>85.22</c:v>
-                </c:pt>
-                <c:pt idx="202">
-                  <c:v>85.22</c:v>
-                </c:pt>
-                <c:pt idx="203">
-                  <c:v>85.34</c:v>
-                </c:pt>
-                <c:pt idx="204">
-                  <c:v>85.47</c:v>
-                </c:pt>
-                <c:pt idx="205">
-                  <c:v>85.64</c:v>
-                </c:pt>
-                <c:pt idx="206">
-                  <c:v>85.64</c:v>
-                </c:pt>
-                <c:pt idx="207">
-                  <c:v>85.78</c:v>
-                </c:pt>
-                <c:pt idx="208">
-                  <c:v>85.91</c:v>
-                </c:pt>
-                <c:pt idx="209">
-                  <c:v>86.08</c:v>
-                </c:pt>
-                <c:pt idx="210">
-                  <c:v>86.08</c:v>
-                </c:pt>
-                <c:pt idx="211">
-                  <c:v>86.17</c:v>
-                </c:pt>
-                <c:pt idx="212">
-                  <c:v>86.33</c:v>
-                </c:pt>
-                <c:pt idx="213">
-                  <c:v>86.47</c:v>
-                </c:pt>
-                <c:pt idx="214">
-                  <c:v>86.47</c:v>
-                </c:pt>
-                <c:pt idx="215">
-                  <c:v>86.59</c:v>
-                </c:pt>
-                <c:pt idx="216">
-                  <c:v>86.72</c:v>
-                </c:pt>
-                <c:pt idx="217">
-                  <c:v>86.84</c:v>
-                </c:pt>
-                <c:pt idx="218">
-                  <c:v>86.97</c:v>
-                </c:pt>
-                <c:pt idx="219">
-                  <c:v>86.97</c:v>
-                </c:pt>
-                <c:pt idx="220">
-                  <c:v>87.09</c:v>
-                </c:pt>
-                <c:pt idx="221">
-                  <c:v>87.22</c:v>
-                </c:pt>
-                <c:pt idx="222">
-                  <c:v>87.34</c:v>
-                </c:pt>
-                <c:pt idx="223">
-                  <c:v>87.34</c:v>
-                </c:pt>
-                <c:pt idx="224">
-                  <c:v>87.47</c:v>
-                </c:pt>
-                <c:pt idx="225">
-                  <c:v>87.59</c:v>
-                </c:pt>
-                <c:pt idx="226">
-                  <c:v>87.72</c:v>
-                </c:pt>
-                <c:pt idx="227">
-                  <c:v>87.72</c:v>
-                </c:pt>
-                <c:pt idx="228">
-                  <c:v>87.84</c:v>
-                </c:pt>
-                <c:pt idx="229">
-                  <c:v>87.97</c:v>
-                </c:pt>
-                <c:pt idx="230">
-                  <c:v>88.04</c:v>
-                </c:pt>
-                <c:pt idx="231">
-                  <c:v>88.04</c:v>
-                </c:pt>
-                <c:pt idx="232">
-                  <c:v>88.16</c:v>
-                </c:pt>
-                <c:pt idx="233">
-                  <c:v>88.28</c:v>
-                </c:pt>
-                <c:pt idx="234">
-                  <c:v>88.41</c:v>
-                </c:pt>
-                <c:pt idx="235">
-                  <c:v>88.41</c:v>
-                </c:pt>
-                <c:pt idx="236">
-                  <c:v>88.48</c:v>
-                </c:pt>
-                <c:pt idx="237">
-                  <c:v>88.6</c:v>
-                </c:pt>
-                <c:pt idx="238">
-                  <c:v>88.72</c:v>
-                </c:pt>
-                <c:pt idx="239">
-                  <c:v>88.72</c:v>
-                </c:pt>
-                <c:pt idx="240">
-                  <c:v>88.84</c:v>
-                </c:pt>
-                <c:pt idx="241">
-                  <c:v>88.92</c:v>
-                </c:pt>
-                <c:pt idx="242">
-                  <c:v>89.03</c:v>
-                </c:pt>
-                <c:pt idx="243">
-                  <c:v>89.03</c:v>
-                </c:pt>
-                <c:pt idx="244">
-                  <c:v>89.16</c:v>
-                </c:pt>
-                <c:pt idx="245">
-                  <c:v>89.23</c:v>
-                </c:pt>
-                <c:pt idx="246">
-                  <c:v>89.35</c:v>
-                </c:pt>
-                <c:pt idx="247">
-                  <c:v>89.42</c:v>
-                </c:pt>
-                <c:pt idx="248">
-                  <c:v>89.42</c:v>
-                </c:pt>
-                <c:pt idx="249">
-                  <c:v>89.53</c:v>
-                </c:pt>
-                <c:pt idx="250">
-                  <c:v>89.61</c:v>
-                </c:pt>
-                <c:pt idx="251">
-                  <c:v>89.72</c:v>
-                </c:pt>
-                <c:pt idx="252">
-                  <c:v>89.72</c:v>
-                </c:pt>
-                <c:pt idx="253">
-                  <c:v>89.84</c:v>
-                </c:pt>
-                <c:pt idx="254">
-                  <c:v>89.92</c:v>
-                </c:pt>
-                <c:pt idx="255">
-                  <c:v>90.03</c:v>
-                </c:pt>
-                <c:pt idx="256">
-                  <c:v>90.03</c:v>
-                </c:pt>
-                <c:pt idx="257">
-                  <c:v>90.11</c:v>
-                </c:pt>
-                <c:pt idx="258">
-                  <c:v>90.22</c:v>
-                </c:pt>
-                <c:pt idx="259">
-                  <c:v>90.29</c:v>
-                </c:pt>
-                <c:pt idx="260">
-                  <c:v>90.29</c:v>
-                </c:pt>
-                <c:pt idx="261">
-                  <c:v>90.41</c:v>
-                </c:pt>
-                <c:pt idx="262">
-                  <c:v>90.53</c:v>
-                </c:pt>
-                <c:pt idx="263">
-                  <c:v>90.61</c:v>
-                </c:pt>
-                <c:pt idx="264">
-                  <c:v>90.61</c:v>
-                </c:pt>
-                <c:pt idx="265">
-                  <c:v>90.67</c:v>
-                </c:pt>
-                <c:pt idx="266">
-                  <c:v>90.73</c:v>
-                </c:pt>
-                <c:pt idx="267">
-                  <c:v>90.85</c:v>
-                </c:pt>
-                <c:pt idx="268">
-                  <c:v>90.85</c:v>
-                </c:pt>
-                <c:pt idx="269">
-                  <c:v>90.92</c:v>
-                </c:pt>
-                <c:pt idx="270">
-                  <c:v>90.98</c:v>
-                </c:pt>
-                <c:pt idx="271">
-                  <c:v>91.05</c:v>
-                </c:pt>
-                <c:pt idx="272">
-                  <c:v>91.16</c:v>
-                </c:pt>
-                <c:pt idx="273">
-                  <c:v>91.16</c:v>
-                </c:pt>
-                <c:pt idx="274">
-                  <c:v>91.23</c:v>
-                </c:pt>
-                <c:pt idx="275">
-                  <c:v>91.3</c:v>
-                </c:pt>
-                <c:pt idx="276">
-                  <c:v>91.41</c:v>
-                </c:pt>
-                <c:pt idx="277">
-                  <c:v>91.41</c:v>
-                </c:pt>
-                <c:pt idx="278">
-                  <c:v>91.48</c:v>
-                </c:pt>
-                <c:pt idx="279">
-                  <c:v>91.6</c:v>
-                </c:pt>
-                <c:pt idx="280">
-                  <c:v>91.67</c:v>
-                </c:pt>
-                <c:pt idx="281">
-                  <c:v>91.67</c:v>
-                </c:pt>
-                <c:pt idx="282">
-                  <c:v>91.73</c:v>
-                </c:pt>
-                <c:pt idx="283">
-                  <c:v>91.8</c:v>
-                </c:pt>
-                <c:pt idx="284">
-                  <c:v>91.86</c:v>
-                </c:pt>
-                <c:pt idx="285">
-                  <c:v>91.86</c:v>
-                </c:pt>
-                <c:pt idx="286">
-                  <c:v>91.97</c:v>
-                </c:pt>
-                <c:pt idx="287">
-                  <c:v>92.04</c:v>
-                </c:pt>
-                <c:pt idx="288">
-                  <c:v>92.11</c:v>
-                </c:pt>
-                <c:pt idx="289">
-                  <c:v>92.11</c:v>
-                </c:pt>
-                <c:pt idx="290">
-                  <c:v>92.22</c:v>
-                </c:pt>
-                <c:pt idx="291">
-                  <c:v>92.29</c:v>
-                </c:pt>
-                <c:pt idx="292">
-                  <c:v>92.36</c:v>
-                </c:pt>
-                <c:pt idx="293">
-                  <c:v>92.42</c:v>
-                </c:pt>
-                <c:pt idx="294">
-                  <c:v>92.42</c:v>
-                </c:pt>
-                <c:pt idx="295">
-                  <c:v>92.48</c:v>
-                </c:pt>
-                <c:pt idx="296">
-                  <c:v>92.55</c:v>
-                </c:pt>
-                <c:pt idx="297">
-                  <c:v>92.66</c:v>
-                </c:pt>
-                <c:pt idx="298">
-                  <c:v>92.66</c:v>
-                </c:pt>
-                <c:pt idx="299">
-                  <c:v>92.68</c:v>
-                </c:pt>
-                <c:pt idx="300">
-                  <c:v>92.74</c:v>
-                </c:pt>
-                <c:pt idx="301">
-                  <c:v>92.85</c:v>
-                </c:pt>
-                <c:pt idx="302">
-                  <c:v>92.85</c:v>
-                </c:pt>
-                <c:pt idx="303">
-                  <c:v>92.87</c:v>
-                </c:pt>
-                <c:pt idx="304">
-                  <c:v>92.97</c:v>
-                </c:pt>
-                <c:pt idx="305">
-                  <c:v>93.04</c:v>
-                </c:pt>
-                <c:pt idx="306">
-                  <c:v>93.04</c:v>
-                </c:pt>
-                <c:pt idx="307">
-                  <c:v>93.11</c:v>
-                </c:pt>
-                <c:pt idx="308">
-                  <c:v>93.17</c:v>
-                </c:pt>
-                <c:pt idx="309">
-                  <c:v>93.23</c:v>
-                </c:pt>
-                <c:pt idx="310">
-                  <c:v>93.23</c:v>
-                </c:pt>
-                <c:pt idx="311">
-                  <c:v>93.3</c:v>
-                </c:pt>
-                <c:pt idx="312">
-                  <c:v>93.36</c:v>
-                </c:pt>
-                <c:pt idx="313">
-                  <c:v>93.47</c:v>
-                </c:pt>
-                <c:pt idx="314">
-                  <c:v>93.49</c:v>
-                </c:pt>
-                <c:pt idx="315">
-                  <c:v>93.49</c:v>
-                </c:pt>
-                <c:pt idx="316">
-                  <c:v>93.55</c:v>
-                </c:pt>
-                <c:pt idx="317">
-                  <c:v>93.61</c:v>
-                </c:pt>
-                <c:pt idx="318">
-                  <c:v>93.67</c:v>
-                </c:pt>
-                <c:pt idx="319">
-                  <c:v>93.67</c:v>
-                </c:pt>
-                <c:pt idx="320">
-                  <c:v>93.73</c:v>
-                </c:pt>
-                <c:pt idx="321">
-                  <c:v>93.85</c:v>
-                </c:pt>
-                <c:pt idx="322">
-                  <c:v>93.87</c:v>
-                </c:pt>
-                <c:pt idx="323">
-                  <c:v>93.87</c:v>
-                </c:pt>
-                <c:pt idx="324">
-                  <c:v>93.97</c:v>
-                </c:pt>
-                <c:pt idx="325">
-                  <c:v>94.04</c:v>
-                </c:pt>
-                <c:pt idx="326">
-                  <c:v>94.11</c:v>
-                </c:pt>
-                <c:pt idx="327">
-                  <c:v>94.11</c:v>
-                </c:pt>
-                <c:pt idx="328">
-                  <c:v>94.17</c:v>
-                </c:pt>
-                <c:pt idx="329">
-                  <c:v>94.23</c:v>
-                </c:pt>
-                <c:pt idx="330">
-                  <c:v>94.3</c:v>
-                </c:pt>
-                <c:pt idx="331">
-                  <c:v>94.3</c:v>
-                </c:pt>
-                <c:pt idx="332">
-                  <c:v>94.31</c:v>
-                </c:pt>
-                <c:pt idx="333">
-                  <c:v>94.41</c:v>
-                </c:pt>
-                <c:pt idx="334">
-                  <c:v>94.41</c:v>
-                </c:pt>
-                <c:pt idx="335">
-                  <c:v>94.48</c:v>
-                </c:pt>
-                <c:pt idx="336">
-                  <c:v>94.55</c:v>
-                </c:pt>
-                <c:pt idx="337">
-                  <c:v>94.61</c:v>
-                </c:pt>
-                <c:pt idx="338">
-                  <c:v>94.67</c:v>
-                </c:pt>
-                <c:pt idx="339">
-                  <c:v>94.68</c:v>
-                </c:pt>
-                <c:pt idx="340">
-                  <c:v>94.68</c:v>
-                </c:pt>
-                <c:pt idx="341">
-                  <c:v>94.74</c:v>
-                </c:pt>
-                <c:pt idx="342">
-                  <c:v>94.74</c:v>
-                </c:pt>
-                <c:pt idx="343">
-                  <c:v>94.87</c:v>
-                </c:pt>
-                <c:pt idx="344">
-                  <c:v>94.87</c:v>
-                </c:pt>
-                <c:pt idx="345">
-                  <c:v>94.92</c:v>
-                </c:pt>
-                <c:pt idx="346">
-                  <c:v>94.98</c:v>
-                </c:pt>
-                <c:pt idx="347">
-                  <c:v>95.05</c:v>
-                </c:pt>
-                <c:pt idx="348">
-                  <c:v>95.05</c:v>
-                </c:pt>
-                <c:pt idx="349">
-                  <c:v>95.11</c:v>
-                </c:pt>
-                <c:pt idx="350">
-                  <c:v>95.17</c:v>
-                </c:pt>
-                <c:pt idx="351">
-                  <c:v>95.23</c:v>
-                </c:pt>
-                <c:pt idx="352">
-                  <c:v>95.23</c:v>
-                </c:pt>
-                <c:pt idx="353">
-                  <c:v>95.25</c:v>
-                </c:pt>
-                <c:pt idx="354">
-                  <c:v>95.3</c:v>
-                </c:pt>
-                <c:pt idx="355">
-                  <c:v>95.36</c:v>
-                </c:pt>
-                <c:pt idx="356">
-                  <c:v>95.42</c:v>
-                </c:pt>
-                <c:pt idx="357">
-                  <c:v>95.42</c:v>
-                </c:pt>
-                <c:pt idx="358">
-                  <c:v>95.48</c:v>
-                </c:pt>
-                <c:pt idx="359">
-                  <c:v>95.55</c:v>
-                </c:pt>
-                <c:pt idx="360">
-                  <c:v>95.56</c:v>
-                </c:pt>
-                <c:pt idx="361">
-                  <c:v>95.56</c:v>
-                </c:pt>
-                <c:pt idx="362">
-                  <c:v>95.66</c:v>
-                </c:pt>
-                <c:pt idx="363">
-                  <c:v>95.66</c:v>
-                </c:pt>
-                <c:pt idx="364">
-                  <c:v>95.74</c:v>
-                </c:pt>
-                <c:pt idx="365">
-                  <c:v>95.74</c:v>
-                </c:pt>
-                <c:pt idx="366">
-                  <c:v>95.8</c:v>
-                </c:pt>
-                <c:pt idx="367">
-                  <c:v>95.86</c:v>
-                </c:pt>
-                <c:pt idx="368">
-                  <c:v>95.92</c:v>
-                </c:pt>
-                <c:pt idx="369">
-                  <c:v>95.92</c:v>
-                </c:pt>
-                <c:pt idx="370">
-                  <c:v>95.93</c:v>
-                </c:pt>
-                <c:pt idx="371">
-                  <c:v>95.99</c:v>
-                </c:pt>
-                <c:pt idx="372">
-                  <c:v>96.05</c:v>
-                </c:pt>
-                <c:pt idx="373">
-                  <c:v>96.05</c:v>
-                </c:pt>
-                <c:pt idx="374">
-                  <c:v>96.11</c:v>
-                </c:pt>
-                <c:pt idx="375">
-                  <c:v>96.17</c:v>
-                </c:pt>
-                <c:pt idx="376">
-                  <c:v>96.18</c:v>
-                </c:pt>
-                <c:pt idx="377">
-                  <c:v>96.18</c:v>
-                </c:pt>
-                <c:pt idx="378">
-                  <c:v>96.24</c:v>
-                </c:pt>
-                <c:pt idx="379">
-                  <c:v>96.3</c:v>
-                </c:pt>
-                <c:pt idx="380">
-                  <c:v>96.31</c:v>
-                </c:pt>
-                <c:pt idx="381">
-                  <c:v>96.36</c:v>
-                </c:pt>
-                <c:pt idx="382">
-                  <c:v>96.36</c:v>
-                </c:pt>
-                <c:pt idx="383">
-                  <c:v>96.42</c:v>
-                </c:pt>
-                <c:pt idx="384">
-                  <c:v>96.48</c:v>
-                </c:pt>
-                <c:pt idx="385">
-                  <c:v>96.55</c:v>
-                </c:pt>
-                <c:pt idx="386">
-                  <c:v>96.55</c:v>
-                </c:pt>
-                <c:pt idx="387">
-                  <c:v>96.61</c:v>
-                </c:pt>
-                <c:pt idx="388">
-                  <c:v>96.62</c:v>
-                </c:pt>
-                <c:pt idx="389">
-                  <c:v>96.67</c:v>
-                </c:pt>
-                <c:pt idx="390">
-                  <c:v>96.67</c:v>
-                </c:pt>
-                <c:pt idx="391">
-                  <c:v>96.73</c:v>
-                </c:pt>
-                <c:pt idx="392">
-                  <c:v>96.75</c:v>
-                </c:pt>
-                <c:pt idx="393">
-                  <c:v>96.75</c:v>
-                </c:pt>
-                <c:pt idx="394">
-                  <c:v>96.8</c:v>
-                </c:pt>
-                <c:pt idx="395">
-                  <c:v>96.86</c:v>
-                </c:pt>
-                <c:pt idx="396">
-                  <c:v>96.87</c:v>
-                </c:pt>
-                <c:pt idx="397">
-                  <c:v>96.92</c:v>
-                </c:pt>
-                <c:pt idx="398">
-                  <c:v>96.92</c:v>
-                </c:pt>
-                <c:pt idx="399">
-                  <c:v>96.98</c:v>
-                </c:pt>
-                <c:pt idx="400">
-                  <c:v>97.05</c:v>
-                </c:pt>
-                <c:pt idx="401">
-                  <c:v>97.06</c:v>
-                </c:pt>
-                <c:pt idx="402">
-                  <c:v>97.11</c:v>
-                </c:pt>
-                <c:pt idx="403">
-                  <c:v>97.11</c:v>
-                </c:pt>
-                <c:pt idx="404">
-                  <c:v>97.17</c:v>
-                </c:pt>
-                <c:pt idx="405">
-                  <c:v>97.18</c:v>
-                </c:pt>
-                <c:pt idx="406">
-                  <c:v>97.24</c:v>
-                </c:pt>
-                <c:pt idx="407">
-                  <c:v>97.24</c:v>
-                </c:pt>
-                <c:pt idx="408">
-                  <c:v>97.25</c:v>
-                </c:pt>
-                <c:pt idx="409">
-                  <c:v>97.3</c:v>
-                </c:pt>
-                <c:pt idx="410">
-                  <c:v>97.36</c:v>
-                </c:pt>
-                <c:pt idx="411">
-                  <c:v>97.36</c:v>
-                </c:pt>
-                <c:pt idx="412">
-                  <c:v>97.37</c:v>
-                </c:pt>
-                <c:pt idx="413">
-                  <c:v>97.42</c:v>
-                </c:pt>
-                <c:pt idx="414">
-                  <c:v>97.48</c:v>
-                </c:pt>
-                <c:pt idx="415">
-                  <c:v>97.48</c:v>
-                </c:pt>
-                <c:pt idx="416">
-                  <c:v>97.55</c:v>
-                </c:pt>
-                <c:pt idx="417">
-                  <c:v>97.56</c:v>
-                </c:pt>
-                <c:pt idx="418">
-                  <c:v>97.61</c:v>
-                </c:pt>
-                <c:pt idx="419">
-                  <c:v>97.61</c:v>
-                </c:pt>
-                <c:pt idx="420">
-                  <c:v>97.62</c:v>
-                </c:pt>
-                <c:pt idx="421">
-                  <c:v>97.67</c:v>
-                </c:pt>
-                <c:pt idx="422">
-                  <c:v>97.73</c:v>
-                </c:pt>
-                <c:pt idx="423">
-                  <c:v>97.75</c:v>
-                </c:pt>
-                <c:pt idx="424">
-                  <c:v>97.75</c:v>
-                </c:pt>
-                <c:pt idx="425">
-                  <c:v>97.8</c:v>
-                </c:pt>
-                <c:pt idx="426">
-                  <c:v>97.86</c:v>
-                </c:pt>
-                <c:pt idx="427">
-                  <c:v>97.87</c:v>
-                </c:pt>
-                <c:pt idx="428">
-                  <c:v>97.87</c:v>
-                </c:pt>
-                <c:pt idx="429">
-                  <c:v>97.92</c:v>
-                </c:pt>
-                <c:pt idx="430">
-                  <c:v>97.98</c:v>
-                </c:pt>
-                <c:pt idx="431">
-                  <c:v>98</c:v>
-                </c:pt>
-                <c:pt idx="432">
-                  <c:v>98</c:v>
-                </c:pt>
-                <c:pt idx="433">
-                  <c:v>98.05</c:v>
-                </c:pt>
-                <c:pt idx="434">
-                  <c:v>98.06</c:v>
-                </c:pt>
-                <c:pt idx="435">
-                  <c:v>98.11</c:v>
-                </c:pt>
-                <c:pt idx="436">
-                  <c:v>98.11</c:v>
-                </c:pt>
-                <c:pt idx="437">
-                  <c:v>98.12</c:v>
-                </c:pt>
-                <c:pt idx="438">
-                  <c:v>98.17</c:v>
-                </c:pt>
-                <c:pt idx="439">
-                  <c:v>98.23</c:v>
-                </c:pt>
-                <c:pt idx="440">
-                  <c:v>98.23</c:v>
-                </c:pt>
-                <c:pt idx="441">
-                  <c:v>98.25</c:v>
-                </c:pt>
-                <c:pt idx="442">
-                  <c:v>98.3</c:v>
-                </c:pt>
-                <c:pt idx="443">
-                  <c:v>98.36</c:v>
-                </c:pt>
-                <c:pt idx="444">
-                  <c:v>98.36</c:v>
-                </c:pt>
-                <c:pt idx="445">
-                  <c:v>98.42</c:v>
-                </c:pt>
-                <c:pt idx="446">
-                  <c:v>98.43</c:v>
-                </c:pt>
-                <c:pt idx="447">
-                  <c:v>98.49</c:v>
-                </c:pt>
-                <c:pt idx="448">
-                  <c:v>98.49</c:v>
-                </c:pt>
-                <c:pt idx="449">
-                  <c:v>98.5</c:v>
-                </c:pt>
-                <c:pt idx="450">
-                  <c:v>98.55</c:v>
-                </c:pt>
-                <c:pt idx="451">
-                  <c:v>98.61</c:v>
-                </c:pt>
-                <c:pt idx="452">
-                  <c:v>98.62</c:v>
-                </c:pt>
-                <c:pt idx="453">
-                  <c:v>98.62</c:v>
-                </c:pt>
-                <c:pt idx="454">
-                  <c:v>98.67</c:v>
-                </c:pt>
-                <c:pt idx="455">
-                  <c:v>98.68</c:v>
-                </c:pt>
-                <c:pt idx="456">
-                  <c:v>98.74</c:v>
-                </c:pt>
-                <c:pt idx="457">
-                  <c:v>98.74</c:v>
-                </c:pt>
-                <c:pt idx="458">
-                  <c:v>98.75</c:v>
-                </c:pt>
-                <c:pt idx="459">
-                  <c:v>98.8</c:v>
-                </c:pt>
-                <c:pt idx="460">
-                  <c:v>98.8</c:v>
-                </c:pt>
-                <c:pt idx="461">
-                  <c:v>98.8</c:v>
-                </c:pt>
-                <c:pt idx="462">
-                  <c:v>98.8</c:v>
-                </c:pt>
-                <c:pt idx="463">
-                  <c:v>98.8</c:v>
-                </c:pt>
-                <c:pt idx="464">
-                  <c:v>98.8</c:v>
-                </c:pt>
-                <c:pt idx="465">
-                  <c:v>98.8</c:v>
-                </c:pt>
-                <c:pt idx="466">
-                  <c:v>98.8</c:v>
-                </c:pt>
-                <c:pt idx="467">
-                  <c:v>98.8</c:v>
-                </c:pt>
-                <c:pt idx="468">
-                  <c:v>98.8</c:v>
-                </c:pt>
-                <c:pt idx="469">
-                  <c:v>98.92</c:v>
-                </c:pt>
-                <c:pt idx="470">
-                  <c:v>98.92</c:v>
-                </c:pt>
-                <c:pt idx="471">
-                  <c:v>98.98</c:v>
-                </c:pt>
-                <c:pt idx="472">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="473">
-                  <c:v>99.05</c:v>
-                </c:pt>
-                <c:pt idx="474">
-                  <c:v>99.05</c:v>
-                </c:pt>
-                <c:pt idx="475">
-                  <c:v>99.11</c:v>
-                </c:pt>
-                <c:pt idx="476">
-                  <c:v>99.12</c:v>
-                </c:pt>
-                <c:pt idx="477">
-                  <c:v>99.17</c:v>
-                </c:pt>
-                <c:pt idx="478">
-                  <c:v>99.17</c:v>
-                </c:pt>
-                <c:pt idx="479">
-                  <c:v>99.18</c:v>
-                </c:pt>
-                <c:pt idx="480">
-                  <c:v>99.19</c:v>
-                </c:pt>
-                <c:pt idx="481">
-                  <c:v>99.24</c:v>
-                </c:pt>
-                <c:pt idx="482">
-                  <c:v>99.24</c:v>
-                </c:pt>
-                <c:pt idx="483">
-                  <c:v>99.3</c:v>
-                </c:pt>
-                <c:pt idx="484">
-                  <c:v>99.31</c:v>
-                </c:pt>
-                <c:pt idx="485">
-                  <c:v>99.36</c:v>
-                </c:pt>
-                <c:pt idx="486">
-                  <c:v>99.36</c:v>
-                </c:pt>
-                <c:pt idx="487">
-                  <c:v>99.37</c:v>
-                </c:pt>
-                <c:pt idx="488">
-                  <c:v>99.42</c:v>
-                </c:pt>
-                <c:pt idx="489">
-                  <c:v>99.43</c:v>
-                </c:pt>
-                <c:pt idx="490">
-                  <c:v>99.49</c:v>
-                </c:pt>
-                <c:pt idx="491">
-                  <c:v>99.49</c:v>
-                </c:pt>
-                <c:pt idx="492">
-                  <c:v>99.5</c:v>
-                </c:pt>
-                <c:pt idx="493">
-                  <c:v>99.5</c:v>
-                </c:pt>
-                <c:pt idx="494">
-                  <c:v>99.5</c:v>
-                </c:pt>
-                <c:pt idx="495">
-                  <c:v>99.55</c:v>
-                </c:pt>
-                <c:pt idx="496">
-                  <c:v>99.56</c:v>
-                </c:pt>
-                <c:pt idx="497">
-                  <c:v>99.61</c:v>
-                </c:pt>
-                <c:pt idx="498">
-                  <c:v>99.62</c:v>
-                </c:pt>
-                <c:pt idx="499">
-                  <c:v>99.62</c:v>
-                </c:pt>
-                <c:pt idx="500">
-                  <c:v>99.67</c:v>
-                </c:pt>
-                <c:pt idx="501">
-                  <c:v>99.68</c:v>
-                </c:pt>
-                <c:pt idx="502">
-                  <c:v>99.74</c:v>
-                </c:pt>
-                <c:pt idx="503">
-                  <c:v>99.74</c:v>
-                </c:pt>
-                <c:pt idx="504">
-                  <c:v>99.75</c:v>
-                </c:pt>
-                <c:pt idx="505">
-                  <c:v>99.75</c:v>
-                </c:pt>
-                <c:pt idx="506">
-                  <c:v>99.75</c:v>
-                </c:pt>
-                <c:pt idx="507">
-                  <c:v>99.75</c:v>
-                </c:pt>
-                <c:pt idx="508">
-                  <c:v>99.75</c:v>
-                </c:pt>
-                <c:pt idx="509">
-                  <c:v>99.8</c:v>
-                </c:pt>
-                <c:pt idx="510">
-                  <c:v>99.86</c:v>
-                </c:pt>
-                <c:pt idx="511">
-                  <c:v>99.87</c:v>
-                </c:pt>
-                <c:pt idx="512">
-                  <c:v>99.87</c:v>
-                </c:pt>
-                <c:pt idx="513">
-                  <c:v>99.92</c:v>
-                </c:pt>
-                <c:pt idx="514">
-                  <c:v>99.93</c:v>
-                </c:pt>
-                <c:pt idx="515">
-                  <c:v>99.99</c:v>
-                </c:pt>
-                <c:pt idx="516">
-                  <c:v>99.99</c:v>
-                </c:pt>
-                <c:pt idx="517">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="518">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="519">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="520">
-                  <c:v>100.05</c:v>
-                </c:pt>
-                <c:pt idx="521">
-                  <c:v>100.11</c:v>
-                </c:pt>
-                <c:pt idx="522">
-                  <c:v>100.12</c:v>
-                </c:pt>
-                <c:pt idx="523">
-                  <c:v>100.17</c:v>
-                </c:pt>
-                <c:pt idx="524">
-                  <c:v>100.17</c:v>
-                </c:pt>
-                <c:pt idx="525">
-                  <c:v>100.18</c:v>
-                </c:pt>
-                <c:pt idx="526">
-                  <c:v>100.24</c:v>
-                </c:pt>
-                <c:pt idx="527">
-                  <c:v>100.25</c:v>
-                </c:pt>
-                <c:pt idx="528">
-                  <c:v>100.25</c:v>
-                </c:pt>
-                <c:pt idx="529">
-                  <c:v>100.3</c:v>
-                </c:pt>
-                <c:pt idx="530">
-                  <c:v>100.31</c:v>
-                </c:pt>
-                <c:pt idx="531">
-                  <c:v>100.36</c:v>
-                </c:pt>
-                <c:pt idx="532">
-                  <c:v>100.36</c:v>
-                </c:pt>
-                <c:pt idx="533">
-                  <c:v>100.37</c:v>
-                </c:pt>
-                <c:pt idx="534">
-                  <c:v>100.42</c:v>
-                </c:pt>
-                <c:pt idx="535">
-                  <c:v>100.43</c:v>
-                </c:pt>
-                <c:pt idx="536">
-                  <c:v>100.49</c:v>
-                </c:pt>
-                <c:pt idx="537">
-                  <c:v>100.49</c:v>
-                </c:pt>
-                <c:pt idx="538">
-                  <c:v>100.5</c:v>
-                </c:pt>
-                <c:pt idx="539">
-                  <c:v>100.5</c:v>
-                </c:pt>
-                <c:pt idx="540">
-                  <c:v>100.55</c:v>
-                </c:pt>
-                <c:pt idx="541">
-                  <c:v>100.55</c:v>
-                </c:pt>
-                <c:pt idx="542">
-                  <c:v>100.56</c:v>
-                </c:pt>
-                <c:pt idx="543">
-                  <c:v>100.56</c:v>
-                </c:pt>
-                <c:pt idx="544">
-                  <c:v>100.56</c:v>
-                </c:pt>
-                <c:pt idx="545">
-                  <c:v>100.56</c:v>
-                </c:pt>
-                <c:pt idx="546">
-                  <c:v>100.56</c:v>
-                </c:pt>
-                <c:pt idx="547">
-                  <c:v>100.56</c:v>
-                </c:pt>
-                <c:pt idx="548">
-                  <c:v>100.56</c:v>
-                </c:pt>
-                <c:pt idx="549">
-                  <c:v>100.68</c:v>
-                </c:pt>
-                <c:pt idx="550">
-                  <c:v>100.74</c:v>
-                </c:pt>
-                <c:pt idx="551">
-                  <c:v>100.75</c:v>
-                </c:pt>
-                <c:pt idx="552">
-                  <c:v>100.75</c:v>
-                </c:pt>
-                <c:pt idx="553">
-                  <c:v>100.75</c:v>
-                </c:pt>
-                <c:pt idx="554">
-                  <c:v>100.8</c:v>
-                </c:pt>
-                <c:pt idx="555">
-                  <c:v>100.86</c:v>
-                </c:pt>
-                <c:pt idx="556">
-                  <c:v>100.87</c:v>
-                </c:pt>
-                <c:pt idx="557">
-                  <c:v>100.87</c:v>
-                </c:pt>
-                <c:pt idx="558">
-                  <c:v>100.87</c:v>
-                </c:pt>
-                <c:pt idx="559">
-                  <c:v>100.87</c:v>
-                </c:pt>
-                <c:pt idx="560">
-                  <c:v>100.92</c:v>
-                </c:pt>
-                <c:pt idx="561">
-                  <c:v>100.93</c:v>
-                </c:pt>
-                <c:pt idx="562">
-                  <c:v>100.93</c:v>
-                </c:pt>
-                <c:pt idx="563">
-                  <c:v>100.94</c:v>
-                </c:pt>
-                <c:pt idx="564">
-                  <c:v>100.94</c:v>
-                </c:pt>
-                <c:pt idx="565">
-                  <c:v>100.94</c:v>
-                </c:pt>
-                <c:pt idx="566">
-                  <c:v>100.94</c:v>
-                </c:pt>
-                <c:pt idx="567">
-                  <c:v>100.99</c:v>
-                </c:pt>
-                <c:pt idx="568">
-                  <c:v>101</c:v>
-                </c:pt>
-                <c:pt idx="569">
-                  <c:v>101</c:v>
-                </c:pt>
-                <c:pt idx="570">
-                  <c:v>101</c:v>
-                </c:pt>
-                <c:pt idx="571">
-                  <c:v>101.05</c:v>
-                </c:pt>
-                <c:pt idx="572">
-                  <c:v>101.06</c:v>
-                </c:pt>
-                <c:pt idx="573">
-                  <c:v>101.11</c:v>
-                </c:pt>
-                <c:pt idx="574">
-                  <c:v>101.11</c:v>
-                </c:pt>
-                <c:pt idx="575">
-                  <c:v>101.12</c:v>
-                </c:pt>
-                <c:pt idx="576">
-                  <c:v>101.12</c:v>
-                </c:pt>
-                <c:pt idx="577">
-                  <c:v>101.17</c:v>
-                </c:pt>
-                <c:pt idx="578">
-                  <c:v>101.17</c:v>
-                </c:pt>
-                <c:pt idx="579">
-                  <c:v>101.18</c:v>
-                </c:pt>
-                <c:pt idx="580">
-                  <c:v>101.24</c:v>
-                </c:pt>
-                <c:pt idx="581">
-                  <c:v>101.25</c:v>
-                </c:pt>
-                <c:pt idx="582">
-                  <c:v>101.25</c:v>
-                </c:pt>
-                <c:pt idx="583">
-                  <c:v>101.25</c:v>
-                </c:pt>
-                <c:pt idx="584">
-                  <c:v>101.3</c:v>
-                </c:pt>
-                <c:pt idx="585">
-                  <c:v>101.36</c:v>
-                </c:pt>
-                <c:pt idx="586">
-                  <c:v>101.37</c:v>
-                </c:pt>
-                <c:pt idx="587">
-                  <c:v>101.37</c:v>
-                </c:pt>
-                <c:pt idx="588">
-                  <c:v>101.37</c:v>
-                </c:pt>
-                <c:pt idx="589">
-                  <c:v>101.42</c:v>
-                </c:pt>
-                <c:pt idx="590">
-                  <c:v>101.43</c:v>
-                </c:pt>
-                <c:pt idx="591">
-                  <c:v>101.43</c:v>
-                </c:pt>
-                <c:pt idx="592">
-                  <c:v>101.44</c:v>
-                </c:pt>
-                <c:pt idx="593">
-                  <c:v>101.49</c:v>
-                </c:pt>
-                <c:pt idx="594">
-                  <c:v>101.49</c:v>
-                </c:pt>
-                <c:pt idx="595">
-                  <c:v>101.5</c:v>
-                </c:pt>
-                <c:pt idx="596">
-                  <c:v>101.5</c:v>
-                </c:pt>
-                <c:pt idx="597">
-                  <c:v>101.5</c:v>
-                </c:pt>
-                <c:pt idx="598">
-                  <c:v>101.55</c:v>
-                </c:pt>
-                <c:pt idx="599">
-                  <c:v>101.56</c:v>
-                </c:pt>
-                <c:pt idx="600">
-                  <c:v>101.56</c:v>
-                </c:pt>
-                <c:pt idx="601">
-                  <c:v>101.61</c:v>
-                </c:pt>
-                <c:pt idx="602">
-                  <c:v>101.62</c:v>
-                </c:pt>
-                <c:pt idx="603">
-                  <c:v>101.62</c:v>
-                </c:pt>
-                <c:pt idx="604">
-                  <c:v>101.62</c:v>
-                </c:pt>
-                <c:pt idx="605">
-                  <c:v>101.67</c:v>
-                </c:pt>
-                <c:pt idx="606">
-                  <c:v>101.68</c:v>
-                </c:pt>
-                <c:pt idx="607">
-                  <c:v>101.69</c:v>
-                </c:pt>
-                <c:pt idx="608">
-                  <c:v>101.69</c:v>
-                </c:pt>
-                <c:pt idx="609">
-                  <c:v>101.74</c:v>
-                </c:pt>
-                <c:pt idx="610">
-                  <c:v>101.75</c:v>
-                </c:pt>
-                <c:pt idx="611">
-                  <c:v>101.75</c:v>
-                </c:pt>
-                <c:pt idx="612">
-                  <c:v>101.75</c:v>
-                </c:pt>
-                <c:pt idx="613">
-                  <c:v>101.75</c:v>
-                </c:pt>
-                <c:pt idx="614">
-                  <c:v>101.8</c:v>
-                </c:pt>
-                <c:pt idx="615">
-                  <c:v>101.86</c:v>
-                </c:pt>
-                <c:pt idx="616">
-                  <c:v>101.86</c:v>
-                </c:pt>
-                <c:pt idx="617">
-                  <c:v>101.87</c:v>
-                </c:pt>
-                <c:pt idx="618">
-                  <c:v>101.87</c:v>
-                </c:pt>
-                <c:pt idx="619">
-                  <c:v>101.92</c:v>
-                </c:pt>
-                <c:pt idx="620">
-                  <c:v>101.93</c:v>
-                </c:pt>
-                <c:pt idx="621">
-                  <c:v>101.93</c:v>
-                </c:pt>
-                <c:pt idx="622">
-                  <c:v>101.94</c:v>
-                </c:pt>
-                <c:pt idx="623">
-                  <c:v>101.99</c:v>
-                </c:pt>
-                <c:pt idx="624">
-                  <c:v>101.99</c:v>
-                </c:pt>
-                <c:pt idx="625">
-                  <c:v>101.99</c:v>
-                </c:pt>
-                <c:pt idx="626">
-                  <c:v>101.99</c:v>
-                </c:pt>
-                <c:pt idx="627">
-                  <c:v>101.99</c:v>
-                </c:pt>
-                <c:pt idx="628">
-                  <c:v>101.99</c:v>
-                </c:pt>
-                <c:pt idx="629">
-                  <c:v>101.99</c:v>
-                </c:pt>
-                <c:pt idx="630">
-                  <c:v>101.99</c:v>
-                </c:pt>
-                <c:pt idx="631">
-                  <c:v>101.99</c:v>
-                </c:pt>
-                <c:pt idx="632">
-                  <c:v>102.12</c:v>
-                </c:pt>
-                <c:pt idx="633">
-                  <c:v>102.17</c:v>
-                </c:pt>
-                <c:pt idx="634">
-                  <c:v>102.18</c:v>
-                </c:pt>
-                <c:pt idx="635">
-                  <c:v>102.18</c:v>
-                </c:pt>
-                <c:pt idx="636">
-                  <c:v>102.24</c:v>
-                </c:pt>
-                <c:pt idx="637">
-                  <c:v>102.25</c:v>
-                </c:pt>
-                <c:pt idx="638">
-                  <c:v>102.25</c:v>
-                </c:pt>
-                <c:pt idx="639">
-                  <c:v>102.25</c:v>
-                </c:pt>
-                <c:pt idx="640">
-                  <c:v>102.25</c:v>
-                </c:pt>
-                <c:pt idx="641">
-                  <c:v>102.3</c:v>
-                </c:pt>
-                <c:pt idx="642">
-                  <c:v>102.31</c:v>
-                </c:pt>
-                <c:pt idx="643">
-                  <c:v>102.31</c:v>
-                </c:pt>
-                <c:pt idx="644">
-                  <c:v>102.31</c:v>
-                </c:pt>
-                <c:pt idx="645">
-                  <c:v>102.36</c:v>
-                </c:pt>
-                <c:pt idx="646">
-                  <c:v>102.37</c:v>
-                </c:pt>
-                <c:pt idx="647">
-                  <c:v>102.37</c:v>
-                </c:pt>
-                <c:pt idx="648">
-                  <c:v>102.37</c:v>
-                </c:pt>
-                <c:pt idx="649">
-                  <c:v>102.37</c:v>
-                </c:pt>
-                <c:pt idx="650">
-                  <c:v>102.37</c:v>
-                </c:pt>
-                <c:pt idx="651">
-                  <c:v>102.42</c:v>
-                </c:pt>
-                <c:pt idx="652">
-                  <c:v>102.42</c:v>
-                </c:pt>
-                <c:pt idx="653">
-                  <c:v>102.43</c:v>
-                </c:pt>
-                <c:pt idx="654">
-                  <c:v>102.49</c:v>
-                </c:pt>
-                <c:pt idx="655">
-                  <c:v>102.5</c:v>
-                </c:pt>
-                <c:pt idx="656">
-                  <c:v>102.5</c:v>
-                </c:pt>
-                <c:pt idx="657">
-                  <c:v>102.5</c:v>
-                </c:pt>
-                <c:pt idx="658">
-                  <c:v>102.5</c:v>
-                </c:pt>
-                <c:pt idx="659">
-                  <c:v>102.55</c:v>
-                </c:pt>
-                <c:pt idx="660">
-                  <c:v>102.55</c:v>
-                </c:pt>
-                <c:pt idx="661">
-                  <c:v>102.56</c:v>
-                </c:pt>
-                <c:pt idx="662">
-                  <c:v>102.56</c:v>
-                </c:pt>
-                <c:pt idx="663">
-                  <c:v>102.61</c:v>
-                </c:pt>
-                <c:pt idx="664">
-                  <c:v>102.61</c:v>
-                </c:pt>
-                <c:pt idx="665">
-                  <c:v>102.62</c:v>
-                </c:pt>
-                <c:pt idx="666">
-                  <c:v>102.62</c:v>
-                </c:pt>
-                <c:pt idx="667">
-                  <c:v>102.67</c:v>
-                </c:pt>
-                <c:pt idx="668">
-                  <c:v>102.68</c:v>
-                </c:pt>
-                <c:pt idx="669">
-                  <c:v>102.68</c:v>
-                </c:pt>
-                <c:pt idx="670">
-                  <c:v>102.74</c:v>
-                </c:pt>
-                <c:pt idx="671">
-                  <c:v>102.75</c:v>
-                </c:pt>
-                <c:pt idx="672">
-                  <c:v>102.8</c:v>
-                </c:pt>
-                <c:pt idx="673">
-                  <c:v>102.8</c:v>
-                </c:pt>
-                <c:pt idx="674">
-                  <c:v>102.81</c:v>
-                </c:pt>
-                <c:pt idx="675">
-                  <c:v>102.81</c:v>
-                </c:pt>
-                <c:pt idx="676">
-                  <c:v>102.86</c:v>
-                </c:pt>
-                <c:pt idx="677">
-                  <c:v>102.86</c:v>
-                </c:pt>
-                <c:pt idx="678">
-                  <c:v>102.87</c:v>
-                </c:pt>
-                <c:pt idx="679">
-                  <c:v>102.87</c:v>
-                </c:pt>
-                <c:pt idx="680">
-                  <c:v>102.92</c:v>
-                </c:pt>
-                <c:pt idx="681">
-                  <c:v>102.92</c:v>
-                </c:pt>
-                <c:pt idx="682">
-                  <c:v>102.93</c:v>
-                </c:pt>
-                <c:pt idx="683">
-                  <c:v>102.94</c:v>
-                </c:pt>
-                <c:pt idx="684">
-                  <c:v>102.99</c:v>
-                </c:pt>
-                <c:pt idx="685">
-                  <c:v>102.99</c:v>
-                </c:pt>
-                <c:pt idx="686">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="687">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="688">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="689">
-                  <c:v>103.05</c:v>
-                </c:pt>
-                <c:pt idx="690">
-                  <c:v>103.06</c:v>
-                </c:pt>
-                <c:pt idx="691">
-                  <c:v>103.06</c:v>
-                </c:pt>
-                <c:pt idx="692">
-                  <c:v>103.06</c:v>
-                </c:pt>
-                <c:pt idx="693">
-                  <c:v>103.11</c:v>
-                </c:pt>
-                <c:pt idx="694">
-                  <c:v>103.11</c:v>
-                </c:pt>
-                <c:pt idx="695">
-                  <c:v>103.12</c:v>
-                </c:pt>
-                <c:pt idx="696">
-                  <c:v>103.12</c:v>
-                </c:pt>
-                <c:pt idx="697">
-                  <c:v>103.17</c:v>
-                </c:pt>
-                <c:pt idx="698">
-                  <c:v>103.17</c:v>
-                </c:pt>
-                <c:pt idx="699">
-                  <c:v>103.18</c:v>
-                </c:pt>
-                <c:pt idx="700">
-                  <c:v>103.19</c:v>
-                </c:pt>
-                <c:pt idx="701">
-                  <c:v>103.24</c:v>
-                </c:pt>
-                <c:pt idx="702">
-                  <c:v>103.24</c:v>
-                </c:pt>
-                <c:pt idx="703">
-                  <c:v>103.25</c:v>
-                </c:pt>
-                <c:pt idx="704">
-                  <c:v>103.25</c:v>
-                </c:pt>
-                <c:pt idx="705">
-                  <c:v>103.25</c:v>
-                </c:pt>
-                <c:pt idx="706">
-                  <c:v>103.3</c:v>
-                </c:pt>
-                <c:pt idx="707">
-                  <c:v>103.3</c:v>
-                </c:pt>
-                <c:pt idx="708">
-                  <c:v>103.3</c:v>
-                </c:pt>
-                <c:pt idx="709">
-                  <c:v>103.3</c:v>
-                </c:pt>
-                <c:pt idx="710">
-                  <c:v>103.3</c:v>
-                </c:pt>
-                <c:pt idx="711">
-                  <c:v>103.3</c:v>
-                </c:pt>
-                <c:pt idx="712">
-                  <c:v>103.3</c:v>
-                </c:pt>
-                <c:pt idx="713">
-                  <c:v>103.3</c:v>
-                </c:pt>
-                <c:pt idx="714">
-                  <c:v>103.3</c:v>
-                </c:pt>
-                <c:pt idx="715">
-                  <c:v>103.3</c:v>
-                </c:pt>
-                <c:pt idx="716">
-                  <c:v>103.3</c:v>
-                </c:pt>
-                <c:pt idx="717">
-                  <c:v>103.3</c:v>
-                </c:pt>
-                <c:pt idx="718">
-                  <c:v>103.42</c:v>
-                </c:pt>
-                <c:pt idx="719">
-                  <c:v>103.42</c:v>
-                </c:pt>
-                <c:pt idx="720">
-                  <c:v>103.42</c:v>
-                </c:pt>
-                <c:pt idx="721">
-                  <c:v>103.42</c:v>
-                </c:pt>
-                <c:pt idx="722">
-                  <c:v>103.43</c:v>
-                </c:pt>
-                <c:pt idx="723">
-                  <c:v>103.49</c:v>
-                </c:pt>
-                <c:pt idx="724">
-                  <c:v>103.5</c:v>
-                </c:pt>
-                <c:pt idx="725">
-                  <c:v>103.5</c:v>
-                </c:pt>
-                <c:pt idx="726">
-                  <c:v>103.55</c:v>
-                </c:pt>
-                <c:pt idx="727">
-                  <c:v>103.56</c:v>
-                </c:pt>
-                <c:pt idx="728">
-                  <c:v>103.61</c:v>
-                </c:pt>
-                <c:pt idx="729">
-                  <c:v>103.62</c:v>
-                </c:pt>
-                <c:pt idx="730">
-                  <c:v>103.62</c:v>
-                </c:pt>
-                <c:pt idx="731">
-                  <c:v>103.62</c:v>
-                </c:pt>
-                <c:pt idx="732">
-                  <c:v>103.67</c:v>
-                </c:pt>
-                <c:pt idx="733">
-                  <c:v>103.68</c:v>
-                </c:pt>
-                <c:pt idx="734">
-                  <c:v>103.68</c:v>
-                </c:pt>
-                <c:pt idx="735">
-                  <c:v>103.74</c:v>
-                </c:pt>
-                <c:pt idx="736">
-                  <c:v>103.75</c:v>
-                </c:pt>
-                <c:pt idx="737">
-                  <c:v>103.75</c:v>
-                </c:pt>
-                <c:pt idx="738">
-                  <c:v>103.75</c:v>
-                </c:pt>
-                <c:pt idx="739">
-                  <c:v>103.8</c:v>
-                </c:pt>
-                <c:pt idx="740">
-                  <c:v>103.81</c:v>
-                </c:pt>
-                <c:pt idx="741">
-                  <c:v>103.81</c:v>
-                </c:pt>
-                <c:pt idx="742">
-                  <c:v>103.81</c:v>
-                </c:pt>
-                <c:pt idx="743">
-                  <c:v>103.86</c:v>
-                </c:pt>
-                <c:pt idx="744">
-                  <c:v>103.87</c:v>
-                </c:pt>
-                <c:pt idx="745">
-                  <c:v>103.87</c:v>
-                </c:pt>
-                <c:pt idx="746">
-                  <c:v>103.87</c:v>
-                </c:pt>
-                <c:pt idx="747">
-                  <c:v>103.92</c:v>
-                </c:pt>
-                <c:pt idx="748">
-                  <c:v>103.88</c:v>
-                </c:pt>
-                <c:pt idx="749">
-                  <c:v>103.93</c:v>
-                </c:pt>
-                <c:pt idx="750">
-                  <c:v>103.93</c:v>
-                </c:pt>
-                <c:pt idx="751">
-                  <c:v>103.94</c:v>
-                </c:pt>
-                <c:pt idx="752">
-                  <c:v>103.94</c:v>
-                </c:pt>
-                <c:pt idx="753">
-                  <c:v>103.99</c:v>
-                </c:pt>
-                <c:pt idx="754">
-                  <c:v>104</c:v>
-                </c:pt>
-                <c:pt idx="755">
-                  <c:v>104</c:v>
-                </c:pt>
-                <c:pt idx="756">
-                  <c:v>104</c:v>
-                </c:pt>
-                <c:pt idx="757">
-                  <c:v>104</c:v>
-                </c:pt>
-                <c:pt idx="758">
-                  <c:v>104</c:v>
-                </c:pt>
-                <c:pt idx="759">
-                  <c:v>104</c:v>
-                </c:pt>
-                <c:pt idx="760">
-                  <c:v>104</c:v>
-                </c:pt>
-                <c:pt idx="761">
-                  <c:v>104</c:v>
-                </c:pt>
-                <c:pt idx="762">
-                  <c:v>104</c:v>
-                </c:pt>
-                <c:pt idx="763">
-                  <c:v>104</c:v>
-                </c:pt>
-                <c:pt idx="764">
-                  <c:v>104.05</c:v>
-                </c:pt>
-                <c:pt idx="765">
-                  <c:v>104.01</c:v>
-                </c:pt>
-                <c:pt idx="766">
-                  <c:v>104.05</c:v>
-                </c:pt>
-                <c:pt idx="767">
-                  <c:v>104.05</c:v>
-                </c:pt>
-                <c:pt idx="768">
-                  <c:v>104.06</c:v>
-                </c:pt>
-                <c:pt idx="769">
-                  <c:v>104.06</c:v>
-                </c:pt>
-                <c:pt idx="770">
-                  <c:v>104.06</c:v>
-                </c:pt>
-                <c:pt idx="771">
-                  <c:v>104.06</c:v>
-                </c:pt>
-                <c:pt idx="772">
-                  <c:v>104.06</c:v>
-                </c:pt>
-                <c:pt idx="773">
-                  <c:v>104.06</c:v>
-                </c:pt>
-                <c:pt idx="774">
-                  <c:v>104.11</c:v>
-                </c:pt>
-                <c:pt idx="775">
-                  <c:v>104.12</c:v>
-                </c:pt>
-                <c:pt idx="776">
-                  <c:v>104.12</c:v>
-                </c:pt>
-                <c:pt idx="777">
-                  <c:v>104.12</c:v>
-                </c:pt>
-                <c:pt idx="778">
-                  <c:v>104.12</c:v>
-                </c:pt>
-                <c:pt idx="779">
-                  <c:v>104.12</c:v>
-                </c:pt>
-                <c:pt idx="780">
-                  <c:v>104.12</c:v>
-                </c:pt>
-                <c:pt idx="781">
-                  <c:v>104.12</c:v>
-                </c:pt>
-                <c:pt idx="782">
-                  <c:v>104.12</c:v>
-                </c:pt>
-                <c:pt idx="783">
-                  <c:v>104.18</c:v>
-                </c:pt>
-                <c:pt idx="784">
-                  <c:v>104.18</c:v>
-                </c:pt>
-                <c:pt idx="785">
-                  <c:v>104.18</c:v>
-                </c:pt>
-                <c:pt idx="786">
-                  <c:v>104.19</c:v>
-                </c:pt>
-                <c:pt idx="787">
-                  <c:v>104.19</c:v>
-                </c:pt>
-                <c:pt idx="788">
-                  <c:v>104.19</c:v>
-                </c:pt>
-                <c:pt idx="789">
-                  <c:v>104.24</c:v>
-                </c:pt>
-                <c:pt idx="790">
-                  <c:v>104.25</c:v>
-                </c:pt>
-                <c:pt idx="791">
-                  <c:v>104.25</c:v>
-                </c:pt>
-                <c:pt idx="792">
-                  <c:v>104.25</c:v>
-                </c:pt>
-                <c:pt idx="793">
-                  <c:v>104.25</c:v>
-                </c:pt>
-                <c:pt idx="794">
-                  <c:v>104.25</c:v>
-                </c:pt>
-                <c:pt idx="795">
-                  <c:v>104.25</c:v>
-                </c:pt>
-                <c:pt idx="796">
-                  <c:v>104.3</c:v>
-                </c:pt>
-                <c:pt idx="797">
-                  <c:v>104.3</c:v>
-                </c:pt>
-                <c:pt idx="798">
-                  <c:v>104.31</c:v>
-                </c:pt>
-                <c:pt idx="799">
-                  <c:v>104.31</c:v>
-                </c:pt>
-                <c:pt idx="800">
-                  <c:v>104.36</c:v>
-                </c:pt>
-                <c:pt idx="801">
-                  <c:v>104.36</c:v>
-                </c:pt>
-                <c:pt idx="802">
-                  <c:v>104.37</c:v>
-                </c:pt>
-                <c:pt idx="803">
-                  <c:v>104.37</c:v>
-                </c:pt>
-                <c:pt idx="804">
-                  <c:v>104.37</c:v>
-                </c:pt>
-                <c:pt idx="805">
-                  <c:v>104.37</c:v>
-                </c:pt>
-                <c:pt idx="806">
-                  <c:v>104.37</c:v>
-                </c:pt>
-                <c:pt idx="807">
-                  <c:v>104.37</c:v>
-                </c:pt>
-                <c:pt idx="808">
-                  <c:v>104.38</c:v>
-                </c:pt>
-                <c:pt idx="809">
-                  <c:v>104.38</c:v>
-                </c:pt>
-                <c:pt idx="810">
-                  <c:v>104.43</c:v>
-                </c:pt>
-                <c:pt idx="811">
-                  <c:v>104.44</c:v>
-                </c:pt>
-                <c:pt idx="812">
-                  <c:v>104.44</c:v>
-                </c:pt>
-                <c:pt idx="813">
-                  <c:v>104.44</c:v>
-                </c:pt>
-                <c:pt idx="814">
-                  <c:v>104.44</c:v>
-                </c:pt>
-                <c:pt idx="815">
-                  <c:v>104.49</c:v>
-                </c:pt>
-                <c:pt idx="816">
-                  <c:v>104.5</c:v>
-                </c:pt>
-                <c:pt idx="817">
-                  <c:v>104.5</c:v>
-                </c:pt>
-                <c:pt idx="818">
-                  <c:v>104.5</c:v>
-                </c:pt>
-                <c:pt idx="819">
-                  <c:v>104.55</c:v>
-                </c:pt>
-                <c:pt idx="820">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="821">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="822">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="823">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="824">
-                  <c:v>104.61</c:v>
-                </c:pt>
-                <c:pt idx="825">
-                  <c:v>104.62</c:v>
-                </c:pt>
-                <c:pt idx="826">
-                  <c:v>104.62</c:v>
-                </c:pt>
-                <c:pt idx="827">
-                  <c:v>104.62</c:v>
-                </c:pt>
-                <c:pt idx="828">
-                  <c:v>104.62</c:v>
-                </c:pt>
-                <c:pt idx="829">
-                  <c:v>104.67</c:v>
-                </c:pt>
-                <c:pt idx="830">
-                  <c:v>104.67</c:v>
-                </c:pt>
-                <c:pt idx="831">
-                  <c:v>104.68</c:v>
-                </c:pt>
-                <c:pt idx="832">
-                  <c:v>104.69</c:v>
-                </c:pt>
-                <c:pt idx="833">
-                  <c:v>104.69</c:v>
-                </c:pt>
-                <c:pt idx="834">
-                  <c:v>104.74</c:v>
-                </c:pt>
-                <c:pt idx="835">
-                  <c:v>104.74</c:v>
-                </c:pt>
-                <c:pt idx="836">
-                  <c:v>104.75</c:v>
-                </c:pt>
-                <c:pt idx="837">
-                  <c:v>104.75</c:v>
-                </c:pt>
-                <c:pt idx="838">
-                  <c:v>104.75</c:v>
-                </c:pt>
-                <c:pt idx="839">
-                  <c:v>104.75</c:v>
-                </c:pt>
-                <c:pt idx="840">
-                  <c:v>104.75</c:v>
-                </c:pt>
-                <c:pt idx="841">
-                  <c:v>104.75</c:v>
-                </c:pt>
-                <c:pt idx="842">
-                  <c:v>104.8</c:v>
-                </c:pt>
-                <c:pt idx="843">
-                  <c:v>104.8</c:v>
-                </c:pt>
-                <c:pt idx="844">
-                  <c:v>104.81</c:v>
-                </c:pt>
-                <c:pt idx="845">
-                  <c:v>104.81</c:v>
-                </c:pt>
-                <c:pt idx="846">
-                  <c:v>104.81</c:v>
-                </c:pt>
-                <c:pt idx="847">
-                  <c:v>104.81</c:v>
-                </c:pt>
-                <c:pt idx="848">
-                  <c:v>104.86</c:v>
-                </c:pt>
-                <c:pt idx="849">
-                  <c:v>104.87</c:v>
-                </c:pt>
-                <c:pt idx="850">
-                  <c:v>104.87</c:v>
-                </c:pt>
-                <c:pt idx="851">
-                  <c:v>104.87</c:v>
-                </c:pt>
-                <c:pt idx="852">
-                  <c:v>104.87</c:v>
-                </c:pt>
-                <c:pt idx="853">
-                  <c:v>104.92</c:v>
-                </c:pt>
-                <c:pt idx="854">
-                  <c:v>104.93</c:v>
-                </c:pt>
-                <c:pt idx="855">
-                  <c:v>104.99</c:v>
-                </c:pt>
-                <c:pt idx="856">
-                  <c:v>104.99</c:v>
-                </c:pt>
-                <c:pt idx="857">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="858">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="859">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="860">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="861">
-                  <c:v>105.05</c:v>
-                </c:pt>
-                <c:pt idx="862">
-                  <c:v>105.06</c:v>
-                </c:pt>
-                <c:pt idx="863">
-                  <c:v>105.06</c:v>
-                </c:pt>
-                <c:pt idx="864">
-                  <c:v>105.06</c:v>
-                </c:pt>
-                <c:pt idx="865">
-                  <c:v>105.11</c:v>
-                </c:pt>
-                <c:pt idx="866">
-                  <c:v>105.11</c:v>
-                </c:pt>
-                <c:pt idx="867">
-                  <c:v>105.12</c:v>
-                </c:pt>
-                <c:pt idx="868">
-                  <c:v>105.12</c:v>
-                </c:pt>
-                <c:pt idx="869">
-                  <c:v>105.12</c:v>
-                </c:pt>
-                <c:pt idx="870">
-                  <c:v>105.12</c:v>
-                </c:pt>
-                <c:pt idx="871">
-                  <c:v>105.12</c:v>
-                </c:pt>
-                <c:pt idx="872">
-                  <c:v>105.12</c:v>
-                </c:pt>
-                <c:pt idx="873">
-                  <c:v>105.17</c:v>
-                </c:pt>
-                <c:pt idx="874">
-                  <c:v>105.18</c:v>
-                </c:pt>
-                <c:pt idx="875">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="876">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="877">
-                  <c:v>105.24</c:v>
-                </c:pt>
-                <c:pt idx="878">
-                  <c:v>105.25</c:v>
-                </c:pt>
-                <c:pt idx="879">
-                  <c:v>105.25</c:v>
-                </c:pt>
-                <c:pt idx="880">
-                  <c:v>105.25</c:v>
-                </c:pt>
-                <c:pt idx="881">
-                  <c:v>105.25</c:v>
-                </c:pt>
-                <c:pt idx="882">
-                  <c:v>105.3</c:v>
-                </c:pt>
-                <c:pt idx="883">
-                  <c:v>105.3</c:v>
-                </c:pt>
-                <c:pt idx="884">
-                  <c:v>105.3</c:v>
-                </c:pt>
-                <c:pt idx="885">
-                  <c:v>105.31</c:v>
-                </c:pt>
-                <c:pt idx="886">
-                  <c:v>105.31</c:v>
-                </c:pt>
-                <c:pt idx="887">
-                  <c:v>105.36</c:v>
-                </c:pt>
-                <c:pt idx="888">
-                  <c:v>105.37</c:v>
-                </c:pt>
-                <c:pt idx="889">
-                  <c:v>105.37</c:v>
-                </c:pt>
-                <c:pt idx="890">
-                  <c:v>105.37</c:v>
-                </c:pt>
-                <c:pt idx="891">
-                  <c:v>105.37</c:v>
-                </c:pt>
-                <c:pt idx="892">
-                  <c:v>105.37</c:v>
-                </c:pt>
-                <c:pt idx="893">
-                  <c:v>105.37</c:v>
-                </c:pt>
-                <c:pt idx="894">
-                  <c:v>105.37</c:v>
-                </c:pt>
-                <c:pt idx="895">
-                  <c:v>105.37</c:v>
-                </c:pt>
-                <c:pt idx="896">
-                  <c:v>105.37</c:v>
-                </c:pt>
-                <c:pt idx="897">
-                  <c:v>105.37</c:v>
-                </c:pt>
-                <c:pt idx="898">
-                  <c:v>105.37</c:v>
-                </c:pt>
-                <c:pt idx="899">
-                  <c:v>105.32</c:v>
-                </c:pt>
-                <c:pt idx="900">
-                  <c:v>105.32</c:v>
-                </c:pt>
-                <c:pt idx="901">
-                  <c:v>105.31</c:v>
-                </c:pt>
-                <c:pt idx="902">
-                  <c:v>105.31</c:v>
-                </c:pt>
-                <c:pt idx="903">
-                  <c:v>105.26</c:v>
-                </c:pt>
-                <c:pt idx="904">
-                  <c:v>105.25</c:v>
-                </c:pt>
-                <c:pt idx="905">
-                  <c:v>105.25</c:v>
-                </c:pt>
-                <c:pt idx="906">
-                  <c:v>105.25</c:v>
-                </c:pt>
-                <c:pt idx="907">
-                  <c:v>105.25</c:v>
-                </c:pt>
-                <c:pt idx="908">
-                  <c:v>105.25</c:v>
-                </c:pt>
-                <c:pt idx="909">
-                  <c:v>105.2</c:v>
-                </c:pt>
-                <c:pt idx="910">
-                  <c:v>105.2</c:v>
-                </c:pt>
-                <c:pt idx="911">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="912">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="913">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="914">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="915">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="916">
-                  <c:v>105.24</c:v>
-                </c:pt>
-                <c:pt idx="917">
-                  <c:v>105.2</c:v>
-                </c:pt>
-                <c:pt idx="918">
-                  <c:v>105.2</c:v>
-                </c:pt>
-                <c:pt idx="919">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="920">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="921">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="922">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="923">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="924">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="925">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="926">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="927">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="928">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="929">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="930">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="931">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="932">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="933">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="934">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="935">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="936">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="937">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="938">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="939">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="940">
-                  <c:v>105.14</c:v>
-                </c:pt>
-                <c:pt idx="941">
-                  <c:v>105.13</c:v>
-                </c:pt>
-                <c:pt idx="942">
-                  <c:v>105.13</c:v>
-                </c:pt>
-                <c:pt idx="943">
-                  <c:v>105.13</c:v>
-                </c:pt>
-                <c:pt idx="944">
-                  <c:v>105.13</c:v>
-                </c:pt>
-                <c:pt idx="945">
-                  <c:v>105.13</c:v>
-                </c:pt>
-                <c:pt idx="946">
-                  <c:v>105.08</c:v>
-                </c:pt>
-                <c:pt idx="947">
-                  <c:v>105.07</c:v>
-                </c:pt>
-                <c:pt idx="948">
-                  <c:v>105.07</c:v>
-                </c:pt>
-                <c:pt idx="949">
-                  <c:v>105.06</c:v>
-                </c:pt>
-                <c:pt idx="950">
-                  <c:v>105.06</c:v>
-                </c:pt>
-                <c:pt idx="951">
-                  <c:v>105.06</c:v>
-                </c:pt>
-                <c:pt idx="952">
-                  <c:v>105.06</c:v>
-                </c:pt>
-                <c:pt idx="953">
-                  <c:v>105.06</c:v>
-                </c:pt>
-                <c:pt idx="954">
-                  <c:v>105.06</c:v>
-                </c:pt>
-                <c:pt idx="955">
-                  <c:v>105.06</c:v>
-                </c:pt>
-                <c:pt idx="956">
-                  <c:v>105.06</c:v>
-                </c:pt>
-                <c:pt idx="957">
-                  <c:v>105.06</c:v>
-                </c:pt>
-                <c:pt idx="958">
-                  <c:v>105.06</c:v>
-                </c:pt>
-                <c:pt idx="959">
-                  <c:v>105.01</c:v>
-                </c:pt>
-                <c:pt idx="960">
-                  <c:v>105.01</c:v>
-                </c:pt>
-                <c:pt idx="961">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="962">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="963">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="964">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="965">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="966">
-                  <c:v>104.95</c:v>
-                </c:pt>
-                <c:pt idx="967">
-                  <c:v>104.94</c:v>
-                </c:pt>
-                <c:pt idx="968">
-                  <c:v>104.94</c:v>
-                </c:pt>
-                <c:pt idx="969">
-                  <c:v>104.94</c:v>
-                </c:pt>
-                <c:pt idx="970">
-                  <c:v>104.94</c:v>
-                </c:pt>
-                <c:pt idx="971">
-                  <c:v>104.89</c:v>
-                </c:pt>
-                <c:pt idx="972">
-                  <c:v>104.88</c:v>
-                </c:pt>
-                <c:pt idx="973">
-                  <c:v>104.88</c:v>
-                </c:pt>
-                <c:pt idx="974">
-                  <c:v>104.88</c:v>
-                </c:pt>
-                <c:pt idx="975">
-                  <c:v>104.83</c:v>
-                </c:pt>
-                <c:pt idx="976">
-                  <c:v>104.82</c:v>
-                </c:pt>
-                <c:pt idx="977">
-                  <c:v>104.82</c:v>
-                </c:pt>
-                <c:pt idx="978">
-                  <c:v>104.76</c:v>
-                </c:pt>
-                <c:pt idx="979">
-                  <c:v>104.75</c:v>
-                </c:pt>
-                <c:pt idx="980">
-                  <c:v>104.75</c:v>
-                </c:pt>
-                <c:pt idx="981">
-                  <c:v>104.75</c:v>
-                </c:pt>
-                <c:pt idx="982">
-                  <c:v>104.7</c:v>
-                </c:pt>
-                <c:pt idx="983">
-                  <c:v>104.64</c:v>
-                </c:pt>
-                <c:pt idx="984">
-                  <c:v>104.63</c:v>
-                </c:pt>
-                <c:pt idx="985">
-                  <c:v>104.63</c:v>
-                </c:pt>
-                <c:pt idx="986">
-                  <c:v>104.63</c:v>
-                </c:pt>
-                <c:pt idx="987">
-                  <c:v>104.58</c:v>
-                </c:pt>
-                <c:pt idx="988">
-                  <c:v>104.57</c:v>
-                </c:pt>
-                <c:pt idx="989">
-                  <c:v>104.57</c:v>
-                </c:pt>
-                <c:pt idx="990">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="991">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="992">
-                  <c:v>104.51</c:v>
-                </c:pt>
-                <c:pt idx="993">
-                  <c:v>104.5</c:v>
-                </c:pt>
-                <c:pt idx="994">
-                  <c:v>104.5</c:v>
-                </c:pt>
-                <c:pt idx="995">
-                  <c:v>104.5</c:v>
-                </c:pt>
-                <c:pt idx="996">
-                  <c:v>104.45</c:v>
-                </c:pt>
-                <c:pt idx="997">
-                  <c:v>104.44</c:v>
-                </c:pt>
-                <c:pt idx="998">
-                  <c:v>104.44</c:v>
-                </c:pt>
-                <c:pt idx="999">
-                  <c:v>104.44</c:v>
-                </c:pt>
-                <c:pt idx="1000">
-                  <c:v>104.44</c:v>
-                </c:pt>
-                <c:pt idx="1001">
-                  <c:v>104.44</c:v>
-                </c:pt>
-                <c:pt idx="1002">
-                  <c:v>104.44</c:v>
-                </c:pt>
-                <c:pt idx="1003">
-                  <c:v>104.44</c:v>
-                </c:pt>
-                <c:pt idx="1004">
-                  <c:v>104.44</c:v>
-                </c:pt>
-                <c:pt idx="1005">
-                  <c:v>104.44</c:v>
-                </c:pt>
-                <c:pt idx="1006">
-                  <c:v>104.44</c:v>
-                </c:pt>
-                <c:pt idx="1007">
-                  <c:v>104.44</c:v>
-                </c:pt>
-                <c:pt idx="1008">
-                  <c:v>104.44</c:v>
-                </c:pt>
-                <c:pt idx="1009">
-                  <c:v>104.49</c:v>
-                </c:pt>
-                <c:pt idx="1010">
-                  <c:v>104.49</c:v>
-                </c:pt>
-                <c:pt idx="1011">
-                  <c:v>104.5</c:v>
-                </c:pt>
-                <c:pt idx="1012">
-                  <c:v>104.5</c:v>
-                </c:pt>
-                <c:pt idx="1013">
-                  <c:v>104.5</c:v>
-                </c:pt>
-                <c:pt idx="1014">
-                  <c:v>104.55</c:v>
-                </c:pt>
-                <c:pt idx="1015">
-                  <c:v>104.55</c:v>
-                </c:pt>
-                <c:pt idx="1016">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="1017">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="1018">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="1019">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="1020">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="1021">
-                  <c:v>104.51</c:v>
-                </c:pt>
-                <c:pt idx="1022">
-                  <c:v>104.5</c:v>
-                </c:pt>
-                <c:pt idx="1023">
-                  <c:v>104.5</c:v>
-                </c:pt>
-                <c:pt idx="1024">
-                  <c:v>104.5</c:v>
-                </c:pt>
-                <c:pt idx="1025">
-                  <c:v>104.5</c:v>
-                </c:pt>
-                <c:pt idx="1026">
-                  <c:v>104.5</c:v>
-                </c:pt>
-                <c:pt idx="1027">
-                  <c:v>104.5</c:v>
-                </c:pt>
-                <c:pt idx="1028">
-                  <c:v>104.5</c:v>
-                </c:pt>
-                <c:pt idx="1029">
-                  <c:v>104.55</c:v>
-                </c:pt>
-                <c:pt idx="1030">
-                  <c:v>104.51</c:v>
-                </c:pt>
-                <c:pt idx="1031">
-                  <c:v>104.51</c:v>
-                </c:pt>
-                <c:pt idx="1032">
-                  <c:v>104.55</c:v>
-                </c:pt>
-                <c:pt idx="1033">
-                  <c:v>104.51</c:v>
-                </c:pt>
-                <c:pt idx="1034">
-                  <c:v>104.55</c:v>
-                </c:pt>
-                <c:pt idx="1035">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="1036">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="1037">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="1038">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="1039">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="1040">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="1041">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="1042">
-                  <c:v>104.56</c:v>
-                </c:pt>
-                <c:pt idx="1043">
-                  <c:v>104.61</c:v>
-                </c:pt>
-                <c:pt idx="1044">
-                  <c:v>104.61</c:v>
-                </c:pt>
-                <c:pt idx="1045">
-                  <c:v>104.62</c:v>
-                </c:pt>
-                <c:pt idx="1046">
-                  <c:v>104.62</c:v>
-                </c:pt>
-                <c:pt idx="1047">
-                  <c:v>104.62</c:v>
-                </c:pt>
-                <c:pt idx="1048">
-                  <c:v>104.62</c:v>
-                </c:pt>
-                <c:pt idx="1049">
-                  <c:v>104.62</c:v>
-                </c:pt>
-                <c:pt idx="1050">
-                  <c:v>104.62</c:v>
-                </c:pt>
-                <c:pt idx="1051">
-                  <c:v>104.67</c:v>
-                </c:pt>
-                <c:pt idx="1052">
-                  <c:v>104.67</c:v>
-                </c:pt>
-                <c:pt idx="1053">
-                  <c:v>104.68</c:v>
-                </c:pt>
-                <c:pt idx="1054">
-                  <c:v>104.69</c:v>
-                </c:pt>
-                <c:pt idx="1055">
-                  <c:v>104.69</c:v>
-                </c:pt>
-                <c:pt idx="1056">
-                  <c:v>104.69</c:v>
-                </c:pt>
-                <c:pt idx="1057">
-                  <c:v>104.69</c:v>
-                </c:pt>
-                <c:pt idx="1058">
-                  <c:v>104.74</c:v>
-                </c:pt>
-                <c:pt idx="1059">
-                  <c:v>104.75</c:v>
-                </c:pt>
-                <c:pt idx="1060">
-                  <c:v>104.75</c:v>
-                </c:pt>
-                <c:pt idx="1061">
-                  <c:v>104.75</c:v>
-                </c:pt>
-                <c:pt idx="1062">
-                  <c:v>104.75</c:v>
-                </c:pt>
-                <c:pt idx="1063">
-                  <c:v>104.75</c:v>
-                </c:pt>
-                <c:pt idx="1064">
-                  <c:v>104.8</c:v>
-                </c:pt>
-                <c:pt idx="1065">
-                  <c:v>104.8</c:v>
-                </c:pt>
-                <c:pt idx="1066">
-                  <c:v>104.81</c:v>
-                </c:pt>
-                <c:pt idx="1067">
-                  <c:v>104.81</c:v>
-                </c:pt>
-                <c:pt idx="1068">
-                  <c:v>104.81</c:v>
-                </c:pt>
-                <c:pt idx="1069">
-                  <c:v>104.81</c:v>
-                </c:pt>
-                <c:pt idx="1070">
-                  <c:v>104.86</c:v>
-                </c:pt>
-                <c:pt idx="1071">
-                  <c:v>104.87</c:v>
-                </c:pt>
-                <c:pt idx="1072">
-                  <c:v>104.87</c:v>
-                </c:pt>
-                <c:pt idx="1073">
-                  <c:v>104.87</c:v>
-                </c:pt>
-                <c:pt idx="1074">
-                  <c:v>104.92</c:v>
-                </c:pt>
-                <c:pt idx="1075">
-                  <c:v>104.93</c:v>
-                </c:pt>
-                <c:pt idx="1076">
-                  <c:v>104.99</c:v>
-                </c:pt>
-                <c:pt idx="1077">
-                  <c:v>104.99</c:v>
-                </c:pt>
-                <c:pt idx="1078">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="1079">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="1080">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="1081">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="1082">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="1083">
-                  <c:v>105.05</c:v>
-                </c:pt>
-                <c:pt idx="1084">
-                  <c:v>105.06</c:v>
-                </c:pt>
-                <c:pt idx="1085">
-                  <c:v>105.06</c:v>
-                </c:pt>
-                <c:pt idx="1086">
-                  <c:v>105.06</c:v>
-                </c:pt>
-                <c:pt idx="1087">
-                  <c:v>105.06</c:v>
-                </c:pt>
-                <c:pt idx="1088">
-                  <c:v>105.11</c:v>
-                </c:pt>
-                <c:pt idx="1089">
-                  <c:v>105.12</c:v>
-                </c:pt>
-                <c:pt idx="1090">
-                  <c:v>105.12</c:v>
-                </c:pt>
-                <c:pt idx="1091">
-                  <c:v>105.12</c:v>
-                </c:pt>
-                <c:pt idx="1092">
-                  <c:v>105.12</c:v>
-                </c:pt>
-                <c:pt idx="1093">
-                  <c:v>105.12</c:v>
-                </c:pt>
-                <c:pt idx="1094">
-                  <c:v>105.12</c:v>
-                </c:pt>
-                <c:pt idx="1095">
-                  <c:v>105.17</c:v>
-                </c:pt>
-                <c:pt idx="1096">
-                  <c:v>105.14</c:v>
-                </c:pt>
-                <c:pt idx="1097">
-                  <c:v>105.18</c:v>
-                </c:pt>
-                <c:pt idx="1098">
-                  <c:v>105.18</c:v>
-                </c:pt>
-                <c:pt idx="1099">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="1100">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="1101">
-                  <c:v>105.19</c:v>
-                </c:pt>
-                <c:pt idx="1102">
-                  <c:v>105.24</c:v>
-                </c:pt>
-                <c:pt idx="1103">
-                  <c:v>105.24</c:v>
-                </c:pt>
-                <c:pt idx="1104">
-                  <c:v>105.2</c:v>
-                </c:pt>
-                <c:pt idx="1105">
-                  <c:v>105.24</c:v>
-                </c:pt>
-                <c:pt idx="1106">
-                  <c:v>105.25</c:v>
-                </c:pt>
-                <c:pt idx="1107">
-                  <c:v>105.25</c:v>
-                </c:pt>
-                <c:pt idx="1108">
-                  <c:v>105.25</c:v>
-                </c:pt>
-                <c:pt idx="1109">
-                  <c:v>105.25</c:v>
-                </c:pt>
-                <c:pt idx="1110">
-                  <c:v>105.3</c:v>
-                </c:pt>
-                <c:pt idx="1111">
-                  <c:v>105.3</c:v>
-                </c:pt>
-                <c:pt idx="1112">
-                  <c:v>105.26</c:v>
-                </c:pt>
-                <c:pt idx="1113">
-                  <c:v>105.3</c:v>
-                </c:pt>
-                <c:pt idx="1114">
-                  <c:v>105.31</c:v>
-                </c:pt>
-                <c:pt idx="1115">
-                  <c:v>105.31</c:v>
-                </c:pt>
-                <c:pt idx="1116">
-                  <c:v>105.31</c:v>
-                </c:pt>
-                <c:pt idx="1117">
-                  <c:v>105.31</c:v>
-                </c:pt>
-                <c:pt idx="1118">
-                  <c:v>105.31</c:v>
-                </c:pt>
-                <c:pt idx="1119">
-                  <c:v>105.31</c:v>
-                </c:pt>
-                <c:pt idx="1120">
-                  <c:v>105.31</c:v>
-                </c:pt>
-                <c:pt idx="1121">
-                  <c:v>105.36</c:v>
-                </c:pt>
-                <c:pt idx="1122">
-                  <c:v>105.37</c:v>
-                </c:pt>
-                <c:pt idx="1123">
-                  <c:v>105.37</c:v>
-                </c:pt>
-                <c:pt idx="1124">
-                  <c:v>105.37</c:v>
-                </c:pt>
-                <c:pt idx="1125">
-                  <c:v>105.37</c:v>
-                </c:pt>
-                <c:pt idx="1126">
-                  <c:v>105.42</c:v>
-                </c:pt>
-                <c:pt idx="1127">
-                  <c:v>105.43</c:v>
-                </c:pt>
-                <c:pt idx="1128">
-                  <c:v>105.43</c:v>
-                </c:pt>
-                <c:pt idx="1129">
-                  <c:v>105.44</c:v>
-                </c:pt>
-                <c:pt idx="1130">
-                  <c:v>105.44</c:v>
-                </c:pt>
-                <c:pt idx="1131">
-                  <c:v>105.49</c:v>
-                </c:pt>
-                <c:pt idx="1132">
-                  <c:v>105.49</c:v>
-                </c:pt>
-                <c:pt idx="1133">
-                  <c:v>105.5</c:v>
-                </c:pt>
-                <c:pt idx="1134">
-                  <c:v>105.5</c:v>
-                </c:pt>
-                <c:pt idx="1135">
-                  <c:v>105.5</c:v>
-                </c:pt>
-                <c:pt idx="1136">
-                  <c:v>105.5</c:v>
-                </c:pt>
-                <c:pt idx="1137">
-                  <c:v>105.5</c:v>
-                </c:pt>
-                <c:pt idx="1138">
-                  <c:v>105.5</c:v>
-                </c:pt>
-                <c:pt idx="1139">
-                  <c:v>105.5</c:v>
-                </c:pt>
-                <c:pt idx="1140">
-                  <c:v>105.5</c:v>
-                </c:pt>
-                <c:pt idx="1141">
-                  <c:v>105.55</c:v>
-                </c:pt>
-                <c:pt idx="1142">
-                  <c:v>105.56</c:v>
-                </c:pt>
-                <c:pt idx="1143">
-                  <c:v>105.56</c:v>
-                </c:pt>
-                <c:pt idx="1144">
-                  <c:v>105.56</c:v>
-                </c:pt>
-                <c:pt idx="1145">
-                  <c:v>105.56</c:v>
-                </c:pt>
-                <c:pt idx="1146">
-                  <c:v>105.61</c:v>
-                </c:pt>
-                <c:pt idx="1147">
-                  <c:v>105.62</c:v>
-                </c:pt>
-                <c:pt idx="1148">
-                  <c:v>105.57</c:v>
-                </c:pt>
-                <c:pt idx="1149">
-                  <c:v>105.57</c:v>
-                </c:pt>
-                <c:pt idx="1150">
-                  <c:v>105.61</c:v>
-                </c:pt>
-                <c:pt idx="1151">
-                  <c:v>105.62</c:v>
-                </c:pt>
-                <c:pt idx="1152">
-                  <c:v>105.62</c:v>
-                </c:pt>
-                <c:pt idx="1153">
-                  <c:v>105.62</c:v>
-                </c:pt>
-                <c:pt idx="1154">
-                  <c:v>105.62</c:v>
-                </c:pt>
-                <c:pt idx="1155">
-                  <c:v>105.67</c:v>
-                </c:pt>
-                <c:pt idx="1156">
-                  <c:v>105.68</c:v>
-                </c:pt>
-                <c:pt idx="1157">
-                  <c:v>105.68</c:v>
-                </c:pt>
-                <c:pt idx="1158">
-                  <c:v>105.69</c:v>
-                </c:pt>
-                <c:pt idx="1159">
-                  <c:v>105.69</c:v>
-                </c:pt>
-                <c:pt idx="1160">
-                  <c:v>105.69</c:v>
-                </c:pt>
-                <c:pt idx="1161">
-                  <c:v>105.69</c:v>
-                </c:pt>
-                <c:pt idx="1162">
-                  <c:v>105.69</c:v>
-                </c:pt>
-                <c:pt idx="1163">
-                  <c:v>105.69</c:v>
-                </c:pt>
-                <c:pt idx="1164">
-                  <c:v>105.74</c:v>
-                </c:pt>
-                <c:pt idx="1165">
-                  <c:v>105.74</c:v>
-                </c:pt>
-                <c:pt idx="1166">
-                  <c:v>105.75</c:v>
-                </c:pt>
-                <c:pt idx="1167">
-                  <c:v>105.75</c:v>
-                </c:pt>
-                <c:pt idx="1168">
-                  <c:v>105.75</c:v>
-                </c:pt>
-                <c:pt idx="1169">
-                  <c:v>105.75</c:v>
-                </c:pt>
-                <c:pt idx="1170">
-                  <c:v>105.75</c:v>
-                </c:pt>
-                <c:pt idx="1171">
-                  <c:v>105.75</c:v>
-                </c:pt>
-                <c:pt idx="1172">
-                  <c:v>105.8</c:v>
-                </c:pt>
-                <c:pt idx="1173">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1174">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1175">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1176">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1177">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1178">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1179">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1180">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1181">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1182">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1183">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1184">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1185">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1186">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1187">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1188">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1189">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1190">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1191">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1192">
-                  <c:v>105.81</c:v>
-                </c:pt>
-                <c:pt idx="1193">
-                  <c:v>105.86</c:v>
-                </c:pt>
-                <c:pt idx="1194">
-                  <c:v>105.87</c:v>
-                </c:pt>
-                <c:pt idx="1195">
-                  <c:v>105.87</c:v>
-                </c:pt>
-                <c:pt idx="1196">
-                  <c:v>105.87</c:v>
-                </c:pt>
-                <c:pt idx="1197">
-                  <c:v>105.87</c:v>
-                </c:pt>
-                <c:pt idx="1198">
-                  <c:v>105.87</c:v>
-                </c:pt>
-                <c:pt idx="1199">
-                  <c:v>105.87</c:v>
-                </c:pt>
-                <c:pt idx="1200">
-                  <c:v>105.92</c:v>
-                </c:pt>
-                <c:pt idx="1201">
-                  <c:v>105.93</c:v>
-                </c:pt>
-                <c:pt idx="1202">
-                  <c:v>105.89</c:v>
-                </c:pt>
-                <c:pt idx="1203">
-                  <c:v>105.89</c:v>
-                </c:pt>
-                <c:pt idx="1204">
-                  <c:v>105.93</c:v>
-                </c:pt>
-                <c:pt idx="1205">
-                  <c:v>105.94</c:v>
-                </c:pt>
-                <c:pt idx="1206">
-                  <c:v>105.94</c:v>
-                </c:pt>
-                <c:pt idx="1207">
-                  <c:v>105.94</c:v>
-                </c:pt>
-                <c:pt idx="1208">
-                  <c:v>105.94</c:v>
-                </c:pt>
-                <c:pt idx="1209">
-                  <c:v>105.94</c:v>
-                </c:pt>
-                <c:pt idx="1210">
-                  <c:v>105.94</c:v>
-                </c:pt>
-                <c:pt idx="1211">
-                  <c:v>105.94</c:v>
-                </c:pt>
-                <c:pt idx="1212">
-                  <c:v>105.94</c:v>
-                </c:pt>
-                <c:pt idx="1213">
-                  <c:v>105.94</c:v>
-                </c:pt>
-                <c:pt idx="1214">
-                  <c:v>105.94</c:v>
-                </c:pt>
-                <c:pt idx="1215">
-                  <c:v>105.94</c:v>
-                </c:pt>
-                <c:pt idx="1216">
-                  <c:v>105.94</c:v>
-                </c:pt>
-                <c:pt idx="1217">
-                  <c:v>105.94</c:v>
-                </c:pt>
-                <c:pt idx="1218">
-                  <c:v>105.99</c:v>
-                </c:pt>
-                <c:pt idx="1219">
-                  <c:v>105.95</c:v>
-                </c:pt>
-                <c:pt idx="1220">
-                  <c:v>105.95</c:v>
-                </c:pt>
-                <c:pt idx="1221">
-                  <c:v>105.99</c:v>
-                </c:pt>
-                <c:pt idx="1222">
-                  <c:v>106</c:v>
-                </c:pt>
-                <c:pt idx="1223">
-                  <c:v>105.95</c:v>
-                </c:pt>
-                <c:pt idx="1224">
-                  <c:v>105.95</c:v>
-                </c:pt>
-                <c:pt idx="1225">
-                  <c:v>105.84</c:v>
-                </c:pt>
-                <c:pt idx="1226">
-                  <c:v>105.67</c:v>
-                </c:pt>
-                <c:pt idx="1227">
-                  <c:v>105.48</c:v>
-                </c:pt>
-                <c:pt idx="1228">
-                  <c:v>105.48</c:v>
-                </c:pt>
-                <c:pt idx="1229">
-                  <c:v>105.2</c:v>
-                </c:pt>
-                <c:pt idx="1230">
-                  <c:v>104.89</c:v>
-                </c:pt>
-                <c:pt idx="1231">
-                  <c:v>104.48</c:v>
-                </c:pt>
-                <c:pt idx="1232">
-                  <c:v>104.48</c:v>
-                </c:pt>
-                <c:pt idx="1233">
-                  <c:v>104.05</c:v>
-                </c:pt>
-                <c:pt idx="1234">
-                  <c:v>103.56</c:v>
-                </c:pt>
-                <c:pt idx="1235">
-                  <c:v>103.06</c:v>
-                </c:pt>
-                <c:pt idx="1236">
-                  <c:v>102.56</c:v>
-                </c:pt>
-                <c:pt idx="1237">
-                  <c:v>102.56</c:v>
-                </c:pt>
-                <c:pt idx="1238">
-                  <c:v>102.01</c:v>
-                </c:pt>
-                <c:pt idx="1239">
-                  <c:v>101.45</c:v>
-                </c:pt>
-                <c:pt idx="1240">
-                  <c:v>100.89</c:v>
-                </c:pt>
-                <c:pt idx="1241">
-                  <c:v>100.89</c:v>
-                </c:pt>
-                <c:pt idx="1242">
-                  <c:v>100.33</c:v>
-                </c:pt>
-                <c:pt idx="1243">
-                  <c:v>99.72</c:v>
-                </c:pt>
-                <c:pt idx="1244">
-                  <c:v>99.14</c:v>
-                </c:pt>
-                <c:pt idx="1245">
-                  <c:v>99.14</c:v>
-                </c:pt>
-                <c:pt idx="1246">
-                  <c:v>98.58</c:v>
-                </c:pt>
-                <c:pt idx="1247">
-                  <c:v>97.97</c:v>
-                </c:pt>
-                <c:pt idx="1248">
-                  <c:v>97.39</c:v>
-                </c:pt>
-                <c:pt idx="1249">
-                  <c:v>97.39</c:v>
-                </c:pt>
-                <c:pt idx="1250">
-                  <c:v>96.78</c:v>
-                </c:pt>
-                <c:pt idx="1251">
-                  <c:v>96.21</c:v>
-                </c:pt>
-                <c:pt idx="1252">
-                  <c:v>95.59</c:v>
-                </c:pt>
-                <c:pt idx="1253">
-                  <c:v>95.59</c:v>
-                </c:pt>
-                <c:pt idx="1254">
-                  <c:v>95.02</c:v>
-                </c:pt>
-                <c:pt idx="1255">
-                  <c:v>94.45</c:v>
-                </c:pt>
-                <c:pt idx="1256">
-                  <c:v>93.84</c:v>
-                </c:pt>
-                <c:pt idx="1257">
-                  <c:v>93.27</c:v>
-                </c:pt>
-                <c:pt idx="1258">
-                  <c:v>93.27</c:v>
-                </c:pt>
-                <c:pt idx="1259">
-                  <c:v>92.7</c:v>
-                </c:pt>
-                <c:pt idx="1260">
-                  <c:v>92.14</c:v>
-                </c:pt>
-                <c:pt idx="1261">
-                  <c:v>91.58</c:v>
-                </c:pt>
-                <c:pt idx="1262">
-                  <c:v>91.58</c:v>
-                </c:pt>
-                <c:pt idx="1263">
-                  <c:v>91.07</c:v>
-                </c:pt>
-                <c:pt idx="1264">
-                  <c:v>90.51</c:v>
-                </c:pt>
-                <c:pt idx="1265">
-                  <c:v>89.95</c:v>
-                </c:pt>
-                <c:pt idx="1266">
-                  <c:v>89.95</c:v>
-                </c:pt>
-                <c:pt idx="1267">
-                  <c:v>89.44</c:v>
-                </c:pt>
-                <c:pt idx="1268">
-                  <c:v>88.94</c:v>
-                </c:pt>
-                <c:pt idx="1269">
-                  <c:v>88.44</c:v>
-                </c:pt>
-                <c:pt idx="1270">
-                  <c:v>88.44</c:v>
-                </c:pt>
-                <c:pt idx="1271">
-                  <c:v>87.94</c:v>
-                </c:pt>
-                <c:pt idx="1272">
-                  <c:v>87.44</c:v>
-                </c:pt>
-                <c:pt idx="1273">
-                  <c:v>86.99</c:v>
-                </c:pt>
-                <c:pt idx="1274">
-                  <c:v>86.99</c:v>
-                </c:pt>
-                <c:pt idx="1275">
-                  <c:v>86.45</c:v>
-                </c:pt>
-                <c:pt idx="1276">
-                  <c:v>85.99</c:v>
-                </c:pt>
-                <c:pt idx="1277">
-                  <c:v>85.5</c:v>
-                </c:pt>
-                <c:pt idx="1278">
-                  <c:v>85.5</c:v>
-                </c:pt>
-                <c:pt idx="1279">
-                  <c:v>85.05</c:v>
-                </c:pt>
-                <c:pt idx="1280">
-                  <c:v>84.56</c:v>
-                </c:pt>
-                <c:pt idx="1281">
-                  <c:v>84.11</c:v>
-                </c:pt>
-                <c:pt idx="1282">
-                  <c:v>83.67</c:v>
-                </c:pt>
-                <c:pt idx="1283">
-                  <c:v>83.67</c:v>
-                </c:pt>
-                <c:pt idx="1284">
-                  <c:v>83.23</c:v>
-                </c:pt>
-                <c:pt idx="1285">
-                  <c:v>82.8</c:v>
-                </c:pt>
-                <c:pt idx="1286">
-                  <c:v>82.36</c:v>
-                </c:pt>
-                <c:pt idx="1287">
-                  <c:v>82.36</c:v>
-                </c:pt>
-                <c:pt idx="1288">
-                  <c:v>81.92</c:v>
-                </c:pt>
-                <c:pt idx="1289">
-                  <c:v>81.48</c:v>
-                </c:pt>
-                <c:pt idx="1290">
-                  <c:v>81.05</c:v>
-                </c:pt>
-                <c:pt idx="1291">
-                  <c:v>81.05</c:v>
-                </c:pt>
-                <c:pt idx="1292">
-                  <c:v>80.66</c:v>
-                </c:pt>
-                <c:pt idx="1293">
-                  <c:v>80.23</c:v>
-                </c:pt>
-                <c:pt idx="1294">
-                  <c:v>79.849999999999994</c:v>
-                </c:pt>
-                <c:pt idx="1295">
-                  <c:v>79.849999999999994</c:v>
-                </c:pt>
-                <c:pt idx="1296">
-                  <c:v>79.42</c:v>
-                </c:pt>
-                <c:pt idx="1297">
-                  <c:v>79.03</c:v>
-                </c:pt>
-                <c:pt idx="1298">
-                  <c:v>78.66</c:v>
-                </c:pt>
-                <c:pt idx="1299">
-                  <c:v>78.66</c:v>
-                </c:pt>
-                <c:pt idx="1300">
-                  <c:v>78.28</c:v>
-                </c:pt>
-                <c:pt idx="1301">
-                  <c:v>77.91</c:v>
-                </c:pt>
-                <c:pt idx="1302">
-                  <c:v>77.53</c:v>
-                </c:pt>
-                <c:pt idx="1303">
-                  <c:v>77.209999999999994</c:v>
-                </c:pt>
-                <c:pt idx="1304">
-                  <c:v>77.209999999999994</c:v>
-                </c:pt>
-                <c:pt idx="1305">
-                  <c:v>76.84</c:v>
-                </c:pt>
-                <c:pt idx="1306">
-                  <c:v>76.47</c:v>
-                </c:pt>
-                <c:pt idx="1307">
-                  <c:v>76.09</c:v>
-                </c:pt>
-                <c:pt idx="1308">
-                  <c:v>76.09</c:v>
-                </c:pt>
-                <c:pt idx="1309">
-                  <c:v>75.77</c:v>
-                </c:pt>
-                <c:pt idx="1310">
-                  <c:v>75.400000000000006</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EEF1-47E5-95E8-8BA1A04948F7}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$D$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PWM1</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$D$2:$D$1312</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1311"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="188">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="189">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="190">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="191">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="192">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="193">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="194">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="195">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="196">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="197">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="198">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="199">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="200">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="201">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="202">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="203">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="204">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="205">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="206">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="207">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="208">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="209">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="210">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="211">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="212">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="213">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="214">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="215">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="216">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="217">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="218">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="219">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="220">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="221">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="222">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="223">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="224">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="225">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="226">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="227">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="228">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="229">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="230">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="231">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="232">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="233">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="234">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="235">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="236">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="237">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="238">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="239">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="240">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="241">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="242">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="243">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="244">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="245">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="246">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="247">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="248">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="249">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="250">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="251">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="252">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="253">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="254">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="255">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="256">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="257">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="258">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="259">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="260">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="261">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="262">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="263">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="264">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="265">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="266">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="267">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="268">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="269">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="270">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="271">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="272">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="273">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="274">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="275">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="276">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="277">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="278">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="279">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="280">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="281">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="282">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="283">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="284">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="285">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="286">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="287">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="288">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="289">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="290">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="291">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="292">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="293">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="294">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="295">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="296">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="297">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="298">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="299">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="300">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="301">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="302">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="303">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="304">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="305">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="306">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="307">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="308">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="309">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="310">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="311">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="312">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="313">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="314">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="315">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="316">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="317">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="318">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="319">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="320">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="321">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="322">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="323">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="324">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="325">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="326">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="327">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="328">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="329">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="330">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="331">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="332">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="333">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="334">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="335">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="336">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="337">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="338">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="339">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="340">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="341">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="342">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="343">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="344">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="345">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="346">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="347">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="348">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="349">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="350">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="351">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="352">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="353">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="354">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="355">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="356">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="357">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="358">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="359">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="360">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="361">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="362">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="363">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="364">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="365">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="366">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="367">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="368">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="369">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="370">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="371">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="372">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="373">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="374">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="375">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="376">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="377">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="378">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="379">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="380">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="381">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="382">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="383">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="384">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="385">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="386">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="387">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="388">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="389">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="390">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="391">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="392">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="393">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="394">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="395">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="396">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="397">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="398">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="399">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="400">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="401">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="402">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="403">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="404">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="405">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="406">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="407">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="408">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="409">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="410">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="411">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="412">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="413">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="414">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="415">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="416">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="417">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="418">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="419">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="420">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="421">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="422">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="423">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="424">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="425">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="426">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="427">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="428">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="429">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="430">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="431">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="432">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="433">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="434">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="435">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="436">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="437">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="438">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="439">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="440">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="441">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="442">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="443">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="444">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="445">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="446">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="447">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="448">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="449">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="450">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="451">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="452">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="453">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="454">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="455">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="456">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="457">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="458">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="459">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="460">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="461">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="462">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="463">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="464">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="465">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="466">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="467">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="468">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="469">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="470">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="471">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="472">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="473">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="474">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="475">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="476">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="477">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="478">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="479">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="480">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="481">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="482">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="483">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="484">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="485">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="486">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="487">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="488">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="489">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="490">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="491">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="492">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="493">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="494">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="495">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="496">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="497">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="498">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="499">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="500">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="501">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="502">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="503">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="504">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="505">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="506">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="507">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="508">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="509">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="510">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="511">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="512">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="513">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="514">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="515">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="516">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="517">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="518">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="519">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="520">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="521">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="522">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="523">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="524">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="525">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="526">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="527">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="528">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="529">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="530">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="531">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="532">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="533">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="534">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="535">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="536">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="537">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="538">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="539">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="540">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="541">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="542">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="543">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="544">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="545">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="546">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="547">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="548">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="549">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="550">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="551">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="552">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="553">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="554">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="555">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="556">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="557">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="558">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="559">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="560">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="561">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="562">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="563">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="564">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="565">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="566">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="567">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="568">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="569">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="570">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="571">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="572">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="573">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="574">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="575">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="576">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="577">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="578">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="579">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="580">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="581">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="582">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="583">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="584">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="585">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="586">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="587">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="588">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="589">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="590">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="591">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="592">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="593">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="594">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="595">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="596">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="597">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="598">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="599">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="600">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="601">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="602">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="603">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="604">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="605">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="606">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="607">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="608">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="609">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="610">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="611">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="612">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="613">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="614">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="615">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="616">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="617">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="618">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="619">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="620">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="621">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="622">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="623">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="624">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="625">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="626">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="627">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="628">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="629">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="630">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="631">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="632">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="633">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="634">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="635">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="636">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="637">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="638">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="639">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="640">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="641">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="642">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="643">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="644">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="645">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="646">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="647">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="648">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="649">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="650">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="651">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="652">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="653">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="654">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="655">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="656">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="657">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="658">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="659">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="660">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="661">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="662">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="663">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="664">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="665">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="666">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="667">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="668">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="669">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="670">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="671">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="672">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="673">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="674">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="675">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="676">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="677">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="678">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="679">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="680">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="681">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="682">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="683">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="684">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="685">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="686">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="687">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="688">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="689">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="690">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="691">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="692">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="693">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="694">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="695">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="696">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="697">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="698">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="699">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="700">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="701">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="702">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="703">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="704">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="705">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="706">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="707">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="708">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="709">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="710">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="711">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="712">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="713">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="714">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="715">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="716">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="717">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="718">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="719">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="720">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="721">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="722">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="723">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="724">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="725">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="726">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="727">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="728">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="729">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="730">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="731">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="732">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="733">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="734">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="735">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="736">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="737">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="738">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="739">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="740">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="741">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="742">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="743">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="744">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="745">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="746">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="747">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="748">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="749">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="750">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="751">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="752">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="753">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="754">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="755">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="756">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="757">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="758">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="759">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="760">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="761">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="762">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="763">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="764">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="765">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="766">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="767">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="768">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="769">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="770">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="771">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="772">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="773">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="774">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="775">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="776">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="777">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="778">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="779">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="780">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="781">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="782">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="783">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="784">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="785">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="786">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="787">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="788">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="789">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="790">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="791">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="792">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="793">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="794">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="795">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="796">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="797">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="798">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="799">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="800">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="801">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="802">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="803">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="804">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="805">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="806">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="807">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="808">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="809">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="810">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="811">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="812">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="813">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="814">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="815">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="816">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="817">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="818">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="819">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="820">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="821">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="822">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="823">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="824">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="825">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="826">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="827">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="828">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="829">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="830">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="831">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="832">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="833">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="834">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="835">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="836">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="837">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="838">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="839">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="840">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="841">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="842">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="843">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="844">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="845">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="846">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="847">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="848">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="849">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="850">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="851">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="852">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="853">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="854">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="855">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="856">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="857">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="858">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="859">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="860">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="861">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="862">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="863">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="864">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="865">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="866">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="867">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="868">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="869">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="870">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="871">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="872">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="873">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="874">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="875">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="876">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="877">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="878">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="879">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="880">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="881">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="882">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="883">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="884">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="885">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="886">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="887">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="888">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="889">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="890">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="891">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="892">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="893">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="894">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="895">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="896">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="897">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="898">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="899">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="900">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="901">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="902">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="903">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="904">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="905">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="906">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="907">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="908">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="909">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="910">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="911">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="912">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="913">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="914">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="915">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="916">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="917">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="918">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="919">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="920">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="921">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="922">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="923">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="924">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="925">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="926">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="927">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="928">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="929">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="930">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="931">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="932">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="933">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="934">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="935">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="936">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="937">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="938">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="939">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="940">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="941">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="942">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="943">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="944">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="945">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="946">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="947">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="948">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="949">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="950">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="951">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="952">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="953">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="954">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="955">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="956">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="957">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="958">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="959">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="960">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="961">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="962">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="963">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="964">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="965">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="966">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="967">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="968">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="969">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="970">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="971">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="972">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="973">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="974">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="975">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="976">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="977">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="978">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="979">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="980">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="981">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="982">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="983">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="984">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="985">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="986">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="987">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="988">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="989">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="990">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="991">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="992">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="993">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="994">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="995">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="996">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="997">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="998">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="999">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1000">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1001">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1002">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1003">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1004">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1005">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1006">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1007">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1008">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1009">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1010">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1011">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1012">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1013">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1014">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1015">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1016">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1017">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1018">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1019">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1020">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1021">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1022">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1023">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1024">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1025">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1026">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1027">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1028">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1029">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1030">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1031">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1032">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1033">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1034">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1035">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1036">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1037">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1038">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1039">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1040">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1041">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1042">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1043">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1044">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1045">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1046">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1047">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1048">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1049">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1050">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1051">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1052">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1053">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1054">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1055">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1056">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1057">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1058">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1059">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1060">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1061">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1062">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1063">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1064">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1065">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1066">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1067">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1068">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1069">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1070">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1071">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1072">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1073">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1074">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1075">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1076">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1077">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1078">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1079">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1080">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1081">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1082">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1083">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1084">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1085">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1086">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1087">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1088">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1089">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1090">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1091">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1092">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1093">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1094">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1095">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1096">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1097">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1098">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1099">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1100">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1101">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1102">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1103">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1104">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1105">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1106">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1107">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1108">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1109">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1110">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1111">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1112">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1113">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1114">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1115">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1116">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1117">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1118">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1119">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1120">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1121">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1122">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1123">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1124">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1125">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1126">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1127">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1128">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1129">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1130">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1131">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1132">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1133">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1134">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1135">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1136">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1137">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1138">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1139">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1140">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1141">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1142">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1143">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1144">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1145">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1146">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1147">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1148">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1149">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1150">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1151">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1152">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1153">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1154">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1155">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1156">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1157">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1158">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1159">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1160">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1161">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1162">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1163">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1164">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1165">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1166">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1167">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1168">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1169">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1170">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1171">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1172">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1173">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1174">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1175">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1176">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1177">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1178">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1179">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1180">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1181">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1182">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1183">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1184">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1185">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1186">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1187">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1188">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1189">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1190">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1191">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1192">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1193">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1194">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1195">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1196">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1197">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1198">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1199">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1200">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1201">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1202">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1203">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1204">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1205">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1206">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1207">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1208">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1209">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1210">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1211">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1212">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1213">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1214">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1215">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1216">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1217">
-                  <c:v>86</c:v>
-                </c:pt>
-                <c:pt idx="1218">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1219">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1220">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1221">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1222">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1223">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1224">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1225">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1226">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1227">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1228">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1229">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1230">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1231">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1232">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1233">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1234">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1235">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1236">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1237">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1238">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1239">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1240">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1241">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1242">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1243">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1244">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1245">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1246">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1247">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1248">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1249">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1250">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1251">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1252">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1253">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1254">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1255">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1256">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1257">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1258">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1259">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1260">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1261">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1262">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1263">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1264">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1265">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1266">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1267">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1268">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1269">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1270">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1271">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1272">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1273">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1274">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1275">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1276">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1277">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1278">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1279">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1280">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1281">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1282">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1283">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1284">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1285">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1286">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1287">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1288">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1289">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1290">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1291">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1292">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1293">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1294">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1295">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1296">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1297">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1298">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1299">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1300">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1301">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1302">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1303">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1304">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1305">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1306">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1307">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1308">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1309">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1310">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EEF1-47E5-95E8-8BA1A04948F7}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="1074618592"/>
-        <c:axId val="1074620672"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1074618592"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1074620672"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1074620672"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1074618592"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="es-CO"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4876800" cy="4981575"/>
     <xdr:pic>
@@ -8904,7 +147,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3200400" y="38100"/>
+          <a:off x="5457825" y="9525"/>
           <a:ext cx="4876800" cy="4981575"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -8914,42 +157,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>90486</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>152399</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Gráfico 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87FEEA83-74B5-4346-86E5-BB8B893F47BD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -9245,7 +452,7 @@
     <col min="20" max="20" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9258,8 +465,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>27</v>
       </c>
@@ -9272,8 +482,19 @@
       <c r="D2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <f>(MAX(B:B)-MIN(B:B))/(_xlfn.MODE.SNGL(D:D)-MIN(D:D))</f>
+        <v>0.76049999999999995</v>
+      </c>
+      <c r="H2">
+        <f>(MAX(B:B)-MIN(B:B))/(MODE(D:D)-MIN(D:D))</f>
+        <v>0.76049999999999995</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>28</v>
       </c>
@@ -9286,8 +507,19 @@
       <c r="D3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3">
+        <f>_xlfn.XLOOKUP(MAX(B:B)*0.632,B:B,A:A,"ajustar valor",-1)-_xlfn.XLOOKUP(_xlfn.MODE.SNGL(D:D),D:D,A:A,"modificar",-1)*1</f>
+        <v>96</v>
+      </c>
+      <c r="H3">
+        <f>INDEX(A:A, MATCH(MAX(B:B)*0.632, B:B)) - INDEX(A:A, MATCH(MODE(D:D), D:D, 0))*1</f>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>28</v>
       </c>
@@ -9300,8 +532,19 @@
       <c r="D4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <f>_xlfn.XLOOKUP(MIN(B:B)*1.02,B:B,A:A,"cambiar",-1)-(_xlfn.XLOOKUP(_xlfn.MODE.SNGL(D:D),D:D,A:A,"modificar",-1))</f>
+        <v>8</v>
+      </c>
+      <c r="H4">
+        <f>INDEX(A:A, MATCH(MIN(B:B)*1.02, B:B)) - (INDEX(A:A, MATCH(MODE(D:D), D:D, 0)))</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>30</v>
       </c>
@@ -9315,7 +558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>31</v>
       </c>
@@ -9329,7 +572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>32</v>
       </c>
@@ -9343,7 +586,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>32</v>
       </c>
@@ -9357,7 +600,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>34</v>
       </c>
@@ -9371,7 +614,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>35</v>
       </c>
@@ -9385,7 +628,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>36</v>
       </c>
@@ -9399,7 +642,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>37</v>
       </c>
@@ -9413,7 +656,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>37</v>
       </c>
@@ -9427,7 +670,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>39</v>
       </c>
@@ -9441,7 +684,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>40</v>
       </c>
@@ -9455,7 +698,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>41</v>
       </c>
@@ -9497,9 +740,6 @@
       <c r="D18">
         <v>100</v>
       </c>
-      <c r="P18" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19">
@@ -9514,13 +754,6 @@
       <c r="D19">
         <v>100</v>
       </c>
-      <c r="O19" t="s">
-        <v>5</v>
-      </c>
-      <c r="P19">
-        <f>(MAX(B:B)-MIN(B:B))/(_xlfn.MODE.SNGL(D:D)-MIN(D:D))</f>
-        <v>0.76049999999999995</v>
-      </c>
       <c r="R19">
         <f>MAX(B:B)</f>
         <v>106</v>
@@ -9539,13 +772,6 @@
       <c r="D20">
         <v>100</v>
       </c>
-      <c r="O20" t="s">
-        <v>7</v>
-      </c>
-      <c r="P20">
-        <f>_xlfn.XLOOKUP(MAX(B:B)*0.632,B:B,A:A,"ajustar valor",-1)-_xlfn.XLOOKUP(_xlfn.MODE.SNGL(D:D),D:D,A:A,"modificar",-1)*1</f>
-        <v>96</v>
-      </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21">
@@ -9559,13 +785,6 @@
       </c>
       <c r="D21">
         <v>100</v>
-      </c>
-      <c r="O21" t="s">
-        <v>6</v>
-      </c>
-      <c r="P21">
-        <f>_xlfn.XLOOKUP(MIN(B:B)*1.02,B:B,A:A,"cambiar",-1)-(_xlfn.XLOOKUP(_xlfn.MODE.SNGL(D:D),D:D,A:A,"modificar",-1))</f>
-        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
